--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">360.104431152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.700225830078</t>
+    <t xml:space="preserve">339.824859619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.7001953125</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675109863281</t>
+    <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.308624267578</t>
+    <t xml:space="preserve">341.151550292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.30859375</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071960449219</t>
+    <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">375.077209472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
@@ -59795,7 +59795,7 @@
     </row>
     <row r="2203">
       <c r="A2203" s="1" t="n">
-        <v>45940.5626273148</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2203" t="n">
         <v>220</v>
@@ -59816,6 +59816,32 @@
         <v>730</v>
       </c>
       <c r="H2203" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" s="1" t="n">
+        <v>45943.5884375</v>
+      </c>
+      <c r="B2204" t="n">
+        <v>219</v>
+      </c>
+      <c r="C2204" t="n">
+        <v>290</v>
+      </c>
+      <c r="D2204" t="n">
+        <v>288</v>
+      </c>
+      <c r="E2204" t="n">
+        <v>289</v>
+      </c>
+      <c r="F2204" t="n">
+        <v>288</v>
+      </c>
+      <c r="G2204" t="s">
+        <v>729</v>
+      </c>
+      <c r="H2204" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104431152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">360.104400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -59,46 +59,46 @@
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.7001953125</t>
+    <t xml:space="preserve">345.700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.138977050781</t>
+    <t xml:space="preserve">342.099212646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">338.119110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366241455078</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438446044922</t>
+    <t xml:space="preserve">350.438415527344</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
+    <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528503417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.071929931641</t>
+    <t xml:space="preserve">370.528533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077209472656</t>
+    <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
@@ -140,22 +140,22 @@
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496032714844</t>
+    <t xml:space="preserve">367.496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
@@ -59821,7 +59821,7 @@
     </row>
     <row r="2204">
       <c r="A2204" s="1" t="n">
-        <v>45943.5884375</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2204" t="n">
         <v>219</v>
@@ -59842,6 +59842,32 @@
         <v>729</v>
       </c>
       <c r="H2204" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" s="1" t="n">
+        <v>45944.5890740741</v>
+      </c>
+      <c r="B2205" t="n">
+        <v>64</v>
+      </c>
+      <c r="C2205" t="n">
+        <v>289</v>
+      </c>
+      <c r="D2205" t="n">
+        <v>289</v>
+      </c>
+      <c r="E2205" t="n">
+        <v>289</v>
+      </c>
+      <c r="F2205" t="n">
+        <v>289</v>
+      </c>
+      <c r="G2205" t="s">
+        <v>730</v>
+      </c>
+      <c r="H2205" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -59847,7 +59847,7 @@
     </row>
     <row r="2205">
       <c r="A2205" s="1" t="n">
-        <v>45944.5890740741</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2205" t="n">
         <v>64</v>
@@ -59868,6 +59868,32 @@
         <v>730</v>
       </c>
       <c r="H2205" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" s="1" t="n">
+        <v>45945.6424537037</v>
+      </c>
+      <c r="B2206" t="n">
+        <v>46</v>
+      </c>
+      <c r="C2206" t="n">
+        <v>289</v>
+      </c>
+      <c r="D2206" t="n">
+        <v>289</v>
+      </c>
+      <c r="E2206" t="n">
+        <v>289</v>
+      </c>
+      <c r="F2206" t="n">
+        <v>289</v>
+      </c>
+      <c r="G2206" t="s">
+        <v>730</v>
+      </c>
+      <c r="H2206" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -65,34 +65,34 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099212646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119110107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366241455078</t>
+    <t xml:space="preserve">342.099182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438415527344</t>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">370.528533935547</t>
+    <t xml:space="preserve">369.580871582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">373.940002441406</t>
+    <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
+    <t xml:space="preserve">361.620666503906</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313812255859</t>
+    <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
@@ -155,13 +155,13 @@
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496002197266</t>
+    <t xml:space="preserve">367.496032714844</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -59873,7 +59873,7 @@
     </row>
     <row r="2206">
       <c r="A2206" s="1" t="n">
-        <v>45945.6424537037</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2206" t="n">
         <v>46</v>
@@ -59894,6 +59894,32 @@
         <v>730</v>
       </c>
       <c r="H2206" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" s="1" t="n">
+        <v>45946.4689583333</v>
+      </c>
+      <c r="B2207" t="n">
+        <v>130</v>
+      </c>
+      <c r="C2207" t="n">
+        <v>291</v>
+      </c>
+      <c r="D2207" t="n">
+        <v>289</v>
+      </c>
+      <c r="E2207" t="n">
+        <v>289</v>
+      </c>
+      <c r="F2207" t="n">
+        <v>289</v>
+      </c>
+      <c r="G2207" t="s">
+        <v>730</v>
+      </c>
+      <c r="H2207" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -59899,10 +59899,10 @@
     </row>
     <row r="2207">
       <c r="A2207" s="1" t="n">
-        <v>45946.4689583333</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2207" t="n">
-        <v>130</v>
+        <v>358</v>
       </c>
       <c r="C2207" t="n">
         <v>291</v>
@@ -59920,6 +59920,32 @@
         <v>730</v>
       </c>
       <c r="H2207" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" s="1" t="n">
+        <v>45947.6197337963</v>
+      </c>
+      <c r="B2208" t="n">
+        <v>52</v>
+      </c>
+      <c r="C2208" t="n">
+        <v>290</v>
+      </c>
+      <c r="D2208" t="n">
+        <v>289</v>
+      </c>
+      <c r="E2208" t="n">
+        <v>289</v>
+      </c>
+      <c r="F2208" t="n">
+        <v>290</v>
+      </c>
+      <c r="G2208" t="s">
+        <v>362</v>
+      </c>
+      <c r="H2208" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="732">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
+    <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
     <t xml:space="preserve">332.622741699219</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
+    <t xml:space="preserve">331.675109863281</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151550292969</t>
+    <t xml:space="preserve">341.151519775391</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
@@ -125,19 +125,19 @@
     <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">373.939971923828</t>
+    <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620666503906</t>
+    <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313842773438</t>
+    <t xml:space="preserve">356.313812255859</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -2205,6 +2205,9 @@
   </si>
   <si>
     <t xml:space="preserve">289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">291</t>
   </si>
 </sst>
 </file>
@@ -59925,7 +59928,7 @@
     </row>
     <row r="2208">
       <c r="A2208" s="1" t="n">
-        <v>45947.6197337963</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2208" t="n">
         <v>52</v>
@@ -59946,6 +59949,32 @@
         <v>362</v>
       </c>
       <c r="H2208" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" s="1" t="n">
+        <v>45950.4035648148</v>
+      </c>
+      <c r="B2209" t="n">
+        <v>72</v>
+      </c>
+      <c r="C2209" t="n">
+        <v>291</v>
+      </c>
+      <c r="D2209" t="n">
+        <v>290</v>
+      </c>
+      <c r="E2209" t="n">
+        <v>290</v>
+      </c>
+      <c r="F2209" t="n">
+        <v>291</v>
+      </c>
+      <c r="G2209" t="s">
+        <v>731</v>
+      </c>
+      <c r="H2209" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -59954,7 +59954,7 @@
     </row>
     <row r="2209">
       <c r="A2209" s="1" t="n">
-        <v>45950.4035648148</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2209" t="n">
         <v>72</v>
@@ -59975,6 +59975,32 @@
         <v>731</v>
       </c>
       <c r="H2209" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" s="1" t="n">
+        <v>45951.6025925926</v>
+      </c>
+      <c r="B2210" t="n">
+        <v>169</v>
+      </c>
+      <c r="C2210" t="n">
+        <v>291</v>
+      </c>
+      <c r="D2210" t="n">
+        <v>289</v>
+      </c>
+      <c r="E2210" t="n">
+        <v>290</v>
+      </c>
+      <c r="F2210" t="n">
+        <v>290</v>
+      </c>
+      <c r="G2210" t="s">
+        <v>362</v>
+      </c>
+      <c r="H2210" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.627990722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">359.914916992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.628021240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622741699219</t>
+    <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
     <t xml:space="preserve">338.119110107422</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675109863281</t>
+    <t xml:space="preserve">331.675170898438</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">355.366180419922</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151519775391</t>
+    <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">347.785064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.940002441406</t>
+    <t xml:space="preserve">369.391326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
+    <t xml:space="preserve">361.620666503906</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313812255859</t>
+    <t xml:space="preserve">356.313873291016</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -59980,7 +59980,7 @@
     </row>
     <row r="2210">
       <c r="A2210" s="1" t="n">
-        <v>45951.6025925926</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2210" t="n">
         <v>169</v>
@@ -60001,6 +60001,32 @@
         <v>362</v>
       </c>
       <c r="H2210" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" s="1" t="n">
+        <v>45952.5865162037</v>
+      </c>
+      <c r="B2211" t="n">
+        <v>63</v>
+      </c>
+      <c r="C2211" t="n">
+        <v>290</v>
+      </c>
+      <c r="D2211" t="n">
+        <v>289</v>
+      </c>
+      <c r="E2211" t="n">
+        <v>289</v>
+      </c>
+      <c r="F2211" t="n">
+        <v>290</v>
+      </c>
+      <c r="G2211" t="s">
+        <v>362</v>
+      </c>
+      <c r="H2211" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914916992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.628021240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">359.914886474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.627990722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622772216797</t>
+    <t xml:space="preserve">332.622741699219</t>
   </si>
   <si>
     <t xml:space="preserve">338.119110107422</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675170898438</t>
+    <t xml:space="preserve">331.675109863281</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.366180419922</t>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151550292969</t>
+    <t xml:space="preserve">341.151519775391</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785064697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">347.785034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.939971923828</t>
+    <t xml:space="preserve">369.391296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620666503906</t>
+    <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313873291016</t>
+    <t xml:space="preserve">356.313812255859</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548431396484</t>
+    <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -60006,7 +60006,7 @@
     </row>
     <row r="2211">
       <c r="A2211" s="1" t="n">
-        <v>45952.5865162037</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2211" t="n">
         <v>63</v>
@@ -60027,6 +60027,32 @@
         <v>362</v>
       </c>
       <c r="H2211" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" s="1" t="n">
+        <v>45953.6343402778</v>
+      </c>
+      <c r="B2212" t="n">
+        <v>441</v>
+      </c>
+      <c r="C2212" t="n">
+        <v>291</v>
+      </c>
+      <c r="D2212" t="n">
+        <v>290</v>
+      </c>
+      <c r="E2212" t="n">
+        <v>291</v>
+      </c>
+      <c r="F2212" t="n">
+        <v>290</v>
+      </c>
+      <c r="G2212" t="s">
+        <v>362</v>
+      </c>
+      <c r="H2212" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -56,7 +56,7 @@
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -65,37 +65,37 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099182128906</t>
+    <t xml:space="preserve">342.099212646484</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622741699219</t>
+    <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
     <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
-    <t xml:space="preserve">345.889770507812</t>
+    <t xml:space="preserve">345.889801025391</t>
   </si>
   <si>
     <t xml:space="preserve">331.675109863281</t>
   </si>
   <si>
-    <t xml:space="preserve">330.727478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">330.727508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366241455078</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.151519775391</t>
+    <t xml:space="preserve">350.438415527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528503417969</t>
+    <t xml:space="preserve">370.528533935547</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496032714844</t>
+    <t xml:space="preserve">367.496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
@@ -60032,7 +60032,7 @@
     </row>
     <row r="2212">
       <c r="A2212" s="1" t="n">
-        <v>45953.6343402778</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2212" t="n">
         <v>441</v>
@@ -60053,6 +60053,32 @@
         <v>362</v>
       </c>
       <c r="H2212" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" s="1" t="n">
+        <v>45954.5907407407</v>
+      </c>
+      <c r="B2213" t="n">
+        <v>99</v>
+      </c>
+      <c r="C2213" t="n">
+        <v>292</v>
+      </c>
+      <c r="D2213" t="n">
+        <v>292</v>
+      </c>
+      <c r="E2213" t="n">
+        <v>292</v>
+      </c>
+      <c r="F2213" t="n">
+        <v>292</v>
+      </c>
+      <c r="G2213" t="s">
+        <v>363</v>
+      </c>
+      <c r="H2213" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -60058,7 +60058,7 @@
     </row>
     <row r="2213">
       <c r="A2213" s="1" t="n">
-        <v>45954.5907407407</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2213" t="n">
         <v>99</v>
@@ -60079,6 +60079,32 @@
         <v>363</v>
       </c>
       <c r="H2213" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" s="1" t="n">
+        <v>45957.6348032407</v>
+      </c>
+      <c r="B2214" t="n">
+        <v>356</v>
+      </c>
+      <c r="C2214" t="n">
+        <v>293</v>
+      </c>
+      <c r="D2214" t="n">
+        <v>291</v>
+      </c>
+      <c r="E2214" t="n">
+        <v>291</v>
+      </c>
+      <c r="F2214" t="n">
+        <v>291</v>
+      </c>
+      <c r="G2214" t="s">
+        <v>731</v>
+      </c>
+      <c r="H2214" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -56,7 +56,7 @@
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -65,37 +65,37 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099212646484</t>
+    <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622772216797</t>
+    <t xml:space="preserve">332.622741699219</t>
   </si>
   <si>
     <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
-    <t xml:space="preserve">345.889801025391</t>
+    <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
     <t xml:space="preserve">331.675109863281</t>
   </si>
   <si>
-    <t xml:space="preserve">330.727508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366241455078</t>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438415527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.151550292969</t>
+    <t xml:space="preserve">350.438446044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.151519775391</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528533935547</t>
+    <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496002197266</t>
+    <t xml:space="preserve">367.496032714844</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
@@ -60084,7 +60084,7 @@
     </row>
     <row r="2214">
       <c r="A2214" s="1" t="n">
-        <v>45957.6348032407</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2214" t="n">
         <v>356</v>
@@ -60105,6 +60105,32 @@
         <v>731</v>
       </c>
       <c r="H2214" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" s="1" t="n">
+        <v>45958.6706828704</v>
+      </c>
+      <c r="B2215" t="n">
+        <v>352</v>
+      </c>
+      <c r="C2215" t="n">
+        <v>291</v>
+      </c>
+      <c r="D2215" t="n">
+        <v>289</v>
+      </c>
+      <c r="E2215" t="n">
+        <v>291</v>
+      </c>
+      <c r="F2215" t="n">
+        <v>290</v>
+      </c>
+      <c r="G2215" t="s">
+        <v>362</v>
+      </c>
+      <c r="H2215" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -56,7 +56,7 @@
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -65,37 +65,37 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099182128906</t>
+    <t xml:space="preserve">342.099212646484</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622741699219</t>
+    <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
     <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
-    <t xml:space="preserve">345.889770507812</t>
+    <t xml:space="preserve">345.889801025391</t>
   </si>
   <si>
     <t xml:space="preserve">331.675109863281</t>
   </si>
   <si>
-    <t xml:space="preserve">330.727478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">330.727508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366241455078</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.151519775391</t>
+    <t xml:space="preserve">350.438415527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528503417969</t>
+    <t xml:space="preserve">370.528533935547</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496032714844</t>
+    <t xml:space="preserve">367.496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
@@ -60110,7 +60110,7 @@
     </row>
     <row r="2215">
       <c r="A2215" s="1" t="n">
-        <v>45958.6706828704</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2215" t="n">
         <v>352</v>
@@ -60131,6 +60131,32 @@
         <v>362</v>
       </c>
       <c r="H2215" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" s="1" t="n">
+        <v>45959.3336342593</v>
+      </c>
+      <c r="B2216" t="n">
+        <v>11</v>
+      </c>
+      <c r="C2216" t="n">
+        <v>291</v>
+      </c>
+      <c r="D2216" t="n">
+        <v>291</v>
+      </c>
+      <c r="E2216" t="n">
+        <v>291</v>
+      </c>
+      <c r="F2216" t="n">
+        <v>291</v>
+      </c>
+      <c r="G2216" t="s">
+        <v>731</v>
+      </c>
+      <c r="H2216" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -65,34 +65,34 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099212646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119110107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366241455078</t>
+    <t xml:space="preserve">342.099182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438415527344</t>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">370.528533935547</t>
+    <t xml:space="preserve">369.580871582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">373.940002441406</t>
+    <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
+    <t xml:space="preserve">361.620666503906</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313812255859</t>
+    <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
@@ -155,13 +155,13 @@
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496002197266</t>
+    <t xml:space="preserve">367.496032714844</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -60136,7 +60136,7 @@
     </row>
     <row r="2216">
       <c r="A2216" s="1" t="n">
-        <v>45959.3336342593</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2216" t="n">
         <v>11</v>
@@ -60157,6 +60157,32 @@
         <v>731</v>
       </c>
       <c r="H2216" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" s="1" t="n">
+        <v>45960.6871990741</v>
+      </c>
+      <c r="B2217" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2217" t="n">
+        <v>290</v>
+      </c>
+      <c r="D2217" t="n">
+        <v>289</v>
+      </c>
+      <c r="E2217" t="n">
+        <v>290</v>
+      </c>
+      <c r="F2217" t="n">
+        <v>289</v>
+      </c>
+      <c r="G2217" t="s">
+        <v>730</v>
+      </c>
+      <c r="H2217" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -53,10 +53,10 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.627990722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">350.628021240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">334.139007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
+    <t xml:space="preserve">331.675170898438</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">355.366180419922</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785034179688</t>
+    <t xml:space="preserve">347.785064697266</t>
   </si>
   <si>
     <t xml:space="preserve">369.580871582031</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391296386719</t>
+    <t xml:space="preserve">369.391326904297</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313842773438</t>
+    <t xml:space="preserve">356.313873291016</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -60162,7 +60162,7 @@
     </row>
     <row r="2217">
       <c r="A2217" s="1" t="n">
-        <v>45960.6871990741</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2217" t="n">
         <v>100</v>
@@ -60183,6 +60183,32 @@
         <v>730</v>
       </c>
       <c r="H2217" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" s="1" t="n">
+        <v>45961.6472222222</v>
+      </c>
+      <c r="B2218" t="n">
+        <v>123</v>
+      </c>
+      <c r="C2218" t="n">
+        <v>289</v>
+      </c>
+      <c r="D2218" t="n">
+        <v>288</v>
+      </c>
+      <c r="E2218" t="n">
+        <v>288</v>
+      </c>
+      <c r="F2218" t="n">
+        <v>289</v>
+      </c>
+      <c r="G2218" t="s">
+        <v>730</v>
+      </c>
+      <c r="H2218" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104400634766</t>
+    <t xml:space="preserve">360.104431152344</t>
   </si>
   <si>
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.628021240234</t>
+    <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.700225830078</t>
+    <t xml:space="preserve">345.7001953125</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
+    <t xml:space="preserve">334.138977050781</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675170898438</t>
+    <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.366180419922</t>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">338.30859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,49 +110,49 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785064697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">347.785034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071960449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.939971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">357.071929931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.940002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077209472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620666503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313873291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">366.548431396484</t>
+    <t xml:space="preserve">361.620635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -60188,7 +60188,7 @@
     </row>
     <row r="2218">
       <c r="A2218" s="1" t="n">
-        <v>45961.6472222222</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2218" t="n">
         <v>123</v>
@@ -60209,6 +60209,32 @@
         <v>730</v>
       </c>
       <c r="H2218" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" s="1" t="n">
+        <v>45964.6910763889</v>
+      </c>
+      <c r="B2219" t="n">
+        <v>1396</v>
+      </c>
+      <c r="C2219" t="n">
+        <v>289</v>
+      </c>
+      <c r="D2219" t="n">
+        <v>284</v>
+      </c>
+      <c r="E2219" t="n">
+        <v>289</v>
+      </c>
+      <c r="F2219" t="n">
+        <v>285</v>
+      </c>
+      <c r="G2219" t="s">
+        <v>370</v>
+      </c>
+      <c r="H2219" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104431152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">360.104400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -59,46 +59,46 @@
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.7001953125</t>
+    <t xml:space="preserve">345.700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.138977050781</t>
+    <t xml:space="preserve">342.099212646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">338.119110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366241455078</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438446044922</t>
+    <t xml:space="preserve">350.438415527344</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
+    <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528503417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.071929931641</t>
+    <t xml:space="preserve">370.528533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077209472656</t>
+    <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
@@ -140,22 +140,22 @@
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496032714844</t>
+    <t xml:space="preserve">367.496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
@@ -60214,7 +60214,7 @@
     </row>
     <row r="2219">
       <c r="A2219" s="1" t="n">
-        <v>45964.6910763889</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2219" t="n">
         <v>1396</v>
@@ -60235,6 +60235,32 @@
         <v>370</v>
       </c>
       <c r="H2219" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" s="1" t="n">
+        <v>45965.5736689815</v>
+      </c>
+      <c r="B2220" t="n">
+        <v>685</v>
+      </c>
+      <c r="C2220" t="n">
+        <v>288</v>
+      </c>
+      <c r="D2220" t="n">
+        <v>282</v>
+      </c>
+      <c r="E2220" t="n">
+        <v>284</v>
+      </c>
+      <c r="F2220" t="n">
+        <v>288</v>
+      </c>
+      <c r="G2220" t="s">
+        <v>729</v>
+      </c>
+      <c r="H2220" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,10 +50,10 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.627990722656</t>
+    <t xml:space="preserve">359.914916992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.628021240234</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099212646484</t>
+    <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
@@ -77,22 +77,22 @@
     <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
-    <t xml:space="preserve">345.889801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366241455078</t>
+    <t xml:space="preserve">345.889770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366180419922</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438415527344</t>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,34 +110,34 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">370.528533935547</t>
+    <t xml:space="preserve">347.785064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580871582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.940002441406</t>
+    <t xml:space="preserve">369.391326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
+    <t xml:space="preserve">361.620666503906</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,22 +146,22 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313812255859</t>
+    <t xml:space="preserve">356.313873291016</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548400878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.496002197266</t>
+    <t xml:space="preserve">366.548431396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.496032714844</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -60240,7 +60240,7 @@
     </row>
     <row r="2220">
       <c r="A2220" s="1" t="n">
-        <v>45965.5736689815</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2220" t="n">
         <v>685</v>
@@ -60261,6 +60261,32 @@
         <v>729</v>
       </c>
       <c r="H2220" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" s="1" t="n">
+        <v>45966.6234375</v>
+      </c>
+      <c r="B2221" t="n">
+        <v>20</v>
+      </c>
+      <c r="C2221" t="n">
+        <v>287</v>
+      </c>
+      <c r="D2221" t="n">
+        <v>285</v>
+      </c>
+      <c r="E2221" t="n">
+        <v>287</v>
+      </c>
+      <c r="F2221" t="n">
+        <v>285</v>
+      </c>
+      <c r="G2221" t="s">
+        <v>370</v>
+      </c>
+      <c r="H2221" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,10 +50,10 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914916992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.628021240234</t>
+    <t xml:space="preserve">359.914886474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099182128906</t>
+    <t xml:space="preserve">342.099212646484</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
@@ -77,22 +77,22 @@
     <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
-    <t xml:space="preserve">345.889770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675170898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366180419922</t>
+    <t xml:space="preserve">345.889801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366241455078</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438446044922</t>
+    <t xml:space="preserve">350.438415527344</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,34 +110,34 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785064697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580871582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">370.528503417969</t>
+    <t xml:space="preserve">347.785034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">370.528533935547</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.939971923828</t>
+    <t xml:space="preserve">369.391296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620666503906</t>
+    <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,22 +146,22 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313873291016</t>
+    <t xml:space="preserve">356.313812255859</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548431396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.496032714844</t>
+    <t xml:space="preserve">366.548400878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -60266,25 +60266,25 @@
     </row>
     <row r="2221">
       <c r="A2221" s="1" t="n">
-        <v>45966.6234375</v>
+        <v>45967.6677893518</v>
       </c>
       <c r="B2221" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="C2221" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D2221" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E2221" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F2221" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G2221" t="s">
-        <v>370</v>
+        <v>727</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -56,7 +56,7 @@
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -65,37 +65,37 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099212646484</t>
+    <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622772216797</t>
+    <t xml:space="preserve">332.622741699219</t>
   </si>
   <si>
     <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
-    <t xml:space="preserve">345.889801025391</t>
+    <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
     <t xml:space="preserve">331.675109863281</t>
   </si>
   <si>
-    <t xml:space="preserve">330.727508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366241455078</t>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438415527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.151550292969</t>
+    <t xml:space="preserve">350.438446044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.151519775391</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528533935547</t>
+    <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496002197266</t>
+    <t xml:space="preserve">367.496032714844</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
@@ -60266,25 +60266,25 @@
     </row>
     <row r="2221">
       <c r="A2221" s="1" t="n">
-        <v>45967.6677893518</v>
+        <v>45968.6635763889</v>
       </c>
       <c r="B2221" t="n">
-        <v>110</v>
+        <v>280</v>
       </c>
       <c r="C2221" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D2221" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E2221" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F2221" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G2221" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">360.104431152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.700225830078</t>
+    <t xml:space="preserve">339.824859619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.7001953125</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675109863281</t>
+    <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.308624267578</t>
+    <t xml:space="preserve">341.151550292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.30859375</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071960449219</t>
+    <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">375.077209472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
@@ -60266,27 +60266,105 @@
     </row>
     <row r="2221">
       <c r="A2221" s="1" t="n">
-        <v>45968.6635763889</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2221" t="n">
-        <v>280</v>
+        <v>20</v>
       </c>
       <c r="C2221" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D2221" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E2221" t="n">
         <v>287</v>
       </c>
       <c r="F2221" t="n">
+        <v>285</v>
+      </c>
+      <c r="G2221" t="s">
+        <v>370</v>
+      </c>
+      <c r="H2221" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2222" t="n">
+        <v>110</v>
+      </c>
+      <c r="C2222" t="n">
+        <v>286</v>
+      </c>
+      <c r="D2222" t="n">
+        <v>286</v>
+      </c>
+      <c r="E2222" t="n">
+        <v>286</v>
+      </c>
+      <c r="F2222" t="n">
+        <v>286</v>
+      </c>
+      <c r="G2222" t="s">
+        <v>727</v>
+      </c>
+      <c r="H2222" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2223" t="n">
+        <v>280</v>
+      </c>
+      <c r="C2223" t="n">
+        <v>288</v>
+      </c>
+      <c r="D2223" t="n">
         <v>287</v>
       </c>
-      <c r="G2221" t="s">
+      <c r="E2223" t="n">
+        <v>287</v>
+      </c>
+      <c r="F2223" t="n">
+        <v>287</v>
+      </c>
+      <c r="G2223" t="s">
         <v>724</v>
       </c>
-      <c r="H2221" t="s">
+      <c r="H2223" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" s="1" t="n">
+        <v>45971.4646296296</v>
+      </c>
+      <c r="B2224" t="n">
+        <v>13</v>
+      </c>
+      <c r="C2224" t="n">
+        <v>287</v>
+      </c>
+      <c r="D2224" t="n">
+        <v>286</v>
+      </c>
+      <c r="E2224" t="n">
+        <v>286</v>
+      </c>
+      <c r="F2224" t="n">
+        <v>287</v>
+      </c>
+      <c r="G2224" t="s">
+        <v>724</v>
+      </c>
+      <c r="H2224" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104431152344</t>
+    <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.627990722656</t>
+    <t xml:space="preserve">350.628021240234</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.7001953125</t>
+    <t xml:space="preserve">345.700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
+    <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
+    <t xml:space="preserve">331.675170898438</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">355.366180419922</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">338.308624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,49 +110,49 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">347.785064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.940002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">357.071960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.939971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">361.620666503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313873291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -60344,7 +60344,7 @@
     </row>
     <row r="2224">
       <c r="A2224" s="1" t="n">
-        <v>45971.4646296296</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2224" t="n">
         <v>13</v>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914916992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.628021240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">359.914886474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.627990722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622772216797</t>
+    <t xml:space="preserve">332.622741699219</t>
   </si>
   <si>
     <t xml:space="preserve">338.119110107422</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675170898438</t>
+    <t xml:space="preserve">331.675109863281</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.366180419922</t>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151550292969</t>
+    <t xml:space="preserve">341.151519775391</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785064697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">347.785034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.939971923828</t>
+    <t xml:space="preserve">369.391296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620666503906</t>
+    <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313873291016</t>
+    <t xml:space="preserve">356.313812255859</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548431396484</t>
+    <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -60368,6 +60368,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2225">
+      <c r="A2225" s="1" t="n">
+        <v>45972.3333333333</v>
+      </c>
+      <c r="B2225" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2225" t="n">
+        <v>287</v>
+      </c>
+      <c r="D2225" t="n">
+        <v>287</v>
+      </c>
+      <c r="E2225" t="n">
+        <v>287</v>
+      </c>
+      <c r="F2225" t="n">
+        <v>287</v>
+      </c>
+      <c r="G2225" t="s">
+        <v>724</v>
+      </c>
+      <c r="H2225" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" s="1" t="n">
+        <v>45973.34375</v>
+      </c>
+      <c r="B2226" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2226" t="n">
+        <v>286</v>
+      </c>
+      <c r="D2226" t="n">
+        <v>286</v>
+      </c>
+      <c r="E2226" t="n">
+        <v>286</v>
+      </c>
+      <c r="F2226" t="n">
+        <v>286</v>
+      </c>
+      <c r="G2226" t="s">
+        <v>727</v>
+      </c>
+      <c r="H2226" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.627990722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">359.914916992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.628021240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622741699219</t>
+    <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
     <t xml:space="preserve">338.119110107422</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675109863281</t>
+    <t xml:space="preserve">331.675170898438</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">355.366180419922</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151519775391</t>
+    <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">347.785064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.940002441406</t>
+    <t xml:space="preserve">369.391326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
+    <t xml:space="preserve">361.620666503906</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313812255859</t>
+    <t xml:space="preserve">356.313873291016</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -60396,7 +60396,7 @@
     </row>
     <row r="2226">
       <c r="A2226" s="1" t="n">
-        <v>45973.34375</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2226" t="n">
         <v>10</v>
@@ -60417,6 +60417,32 @@
         <v>727</v>
       </c>
       <c r="H2226" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" s="1" t="n">
+        <v>45974.4946759259</v>
+      </c>
+      <c r="B2227" t="n">
+        <v>130</v>
+      </c>
+      <c r="C2227" t="n">
+        <v>287</v>
+      </c>
+      <c r="D2227" t="n">
+        <v>286</v>
+      </c>
+      <c r="E2227" t="n">
+        <v>287</v>
+      </c>
+      <c r="F2227" t="n">
+        <v>286</v>
+      </c>
+      <c r="G2227" t="s">
+        <v>727</v>
+      </c>
+      <c r="H2227" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914916992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.628021240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">359.914886474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.627990722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622772216797</t>
+    <t xml:space="preserve">332.622741699219</t>
   </si>
   <si>
     <t xml:space="preserve">338.119110107422</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675170898438</t>
+    <t xml:space="preserve">331.675109863281</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.366180419922</t>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151550292969</t>
+    <t xml:space="preserve">341.151519775391</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785064697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">347.785034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.939971923828</t>
+    <t xml:space="preserve">369.391296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620666503906</t>
+    <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313873291016</t>
+    <t xml:space="preserve">356.313812255859</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548431396484</t>
+    <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -60422,7 +60422,7 @@
     </row>
     <row r="2227">
       <c r="A2227" s="1" t="n">
-        <v>45974.4946759259</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2227" t="n">
         <v>130</v>
@@ -60443,6 +60443,32 @@
         <v>727</v>
       </c>
       <c r="H2227" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" s="1" t="n">
+        <v>45975.659849537</v>
+      </c>
+      <c r="B2228" t="n">
+        <v>295</v>
+      </c>
+      <c r="C2228" t="n">
+        <v>290</v>
+      </c>
+      <c r="D2228" t="n">
+        <v>287</v>
+      </c>
+      <c r="E2228" t="n">
+        <v>287</v>
+      </c>
+      <c r="F2228" t="n">
+        <v>288</v>
+      </c>
+      <c r="G2228" t="s">
+        <v>729</v>
+      </c>
+      <c r="H2228" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">360.104431152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.700225830078</t>
+    <t xml:space="preserve">339.824859619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.7001953125</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675109863281</t>
+    <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.308624267578</t>
+    <t xml:space="preserve">341.151550292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.30859375</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071960449219</t>
+    <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">375.077209472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
@@ -60448,7 +60448,7 @@
     </row>
     <row r="2228">
       <c r="A2228" s="1" t="n">
-        <v>45975.659849537</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2228" t="n">
         <v>295</v>
@@ -60469,6 +60469,32 @@
         <v>729</v>
       </c>
       <c r="H2228" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" s="1" t="n">
+        <v>45978.546412037</v>
+      </c>
+      <c r="B2229" t="n">
+        <v>111</v>
+      </c>
+      <c r="C2229" t="n">
+        <v>289</v>
+      </c>
+      <c r="D2229" t="n">
+        <v>288</v>
+      </c>
+      <c r="E2229" t="n">
+        <v>289</v>
+      </c>
+      <c r="F2229" t="n">
+        <v>288</v>
+      </c>
+      <c r="G2229" t="s">
+        <v>729</v>
+      </c>
+      <c r="H2229" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104431152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">360.104400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824859619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.7001953125</t>
+    <t xml:space="preserve">339.824829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">334.139007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
+    <t xml:space="preserve">331.675109863281</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151550292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.30859375</t>
+    <t xml:space="preserve">341.151519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071929931641</t>
+    <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">375.077178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
@@ -60474,7 +60474,7 @@
     </row>
     <row r="2229">
       <c r="A2229" s="1" t="n">
-        <v>45978.546412037</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2229" t="n">
         <v>111</v>
@@ -60495,6 +60495,32 @@
         <v>729</v>
       </c>
       <c r="H2229" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" s="1" t="n">
+        <v>45979.691099537</v>
+      </c>
+      <c r="B2230" t="n">
+        <v>68</v>
+      </c>
+      <c r="C2230" t="n">
+        <v>289</v>
+      </c>
+      <c r="D2230" t="n">
+        <v>287</v>
+      </c>
+      <c r="E2230" t="n">
+        <v>287</v>
+      </c>
+      <c r="F2230" t="n">
+        <v>287</v>
+      </c>
+      <c r="G2230" t="s">
+        <v>724</v>
+      </c>
+      <c r="H2230" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,19 +44,19 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398651123047</t>
+    <t xml:space="preserve">358.398681640625</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -71,34 +71,34 @@
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">332.622772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727478027344</t>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727447509766</t>
   </si>
   <si>
     <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">343.804931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.438446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.151519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.308624267578</t>
+    <t xml:space="preserve">343.804962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.4384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.151550292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.30859375</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046813964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785034179688</t>
+    <t xml:space="preserve">343.046844482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785064697266</t>
   </si>
   <si>
     <t xml:space="preserve">369.580841064453</t>
@@ -119,37 +119,37 @@
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071960449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.940002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">371.476135253906</t>
+    <t xml:space="preserve">357.071929931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.939971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077209472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">371.476165771484</t>
   </si>
   <si>
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -60500,7 +60500,7 @@
     </row>
     <row r="2230">
       <c r="A2230" s="1" t="n">
-        <v>45979.691099537</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2230" t="n">
         <v>68</v>
@@ -60521,6 +60521,32 @@
         <v>724</v>
       </c>
       <c r="H2230" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" s="1" t="n">
+        <v>45980.6805902778</v>
+      </c>
+      <c r="B2231" t="n">
+        <v>358</v>
+      </c>
+      <c r="C2231" t="n">
+        <v>288</v>
+      </c>
+      <c r="D2231" t="n">
+        <v>287</v>
+      </c>
+      <c r="E2231" t="n">
+        <v>288</v>
+      </c>
+      <c r="F2231" t="n">
+        <v>287</v>
+      </c>
+      <c r="G2231" t="s">
+        <v>724</v>
+      </c>
+      <c r="H2231" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398681640625</t>
+    <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.627990722656</t>
+    <t xml:space="preserve">350.628021240234</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
@@ -74,52 +74,52 @@
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727447509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.804962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.4384765625</t>
+    <t xml:space="preserve">331.675170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366180419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.804931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">338.308624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046844482422</t>
+    <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
     <t xml:space="preserve">347.785064697266</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071929931641</t>
+    <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
     <t xml:space="preserve">369.391326904297</t>
@@ -128,31 +128,31 @@
     <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875122070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">371.476165771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">361.620635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">375.077178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875091552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">371.476135253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">361.620666503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313873291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -60526,7 +60526,7 @@
     </row>
     <row r="2231">
       <c r="A2231" s="1" t="n">
-        <v>45980.6805902778</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2231" t="n">
         <v>358</v>
@@ -60547,6 +60547,32 @@
         <v>724</v>
       </c>
       <c r="H2231" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" s="1" t="n">
+        <v>45981.5623958333</v>
+      </c>
+      <c r="B2232" t="n">
+        <v>33</v>
+      </c>
+      <c r="C2232" t="n">
+        <v>290</v>
+      </c>
+      <c r="D2232" t="n">
+        <v>288</v>
+      </c>
+      <c r="E2232" t="n">
+        <v>290</v>
+      </c>
+      <c r="F2232" t="n">
+        <v>290</v>
+      </c>
+      <c r="G2232" t="s">
+        <v>362</v>
+      </c>
+      <c r="H2232" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -53,10 +53,10 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.628021240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">350.627990722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675170898438</t>
+    <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.366180419922</t>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785064697266</t>
+    <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">369.580871582031</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391326904297</t>
+    <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313873291016</t>
+    <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548431396484</t>
+    <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -60552,7 +60552,7 @@
     </row>
     <row r="2232">
       <c r="A2232" s="1" t="n">
-        <v>45981.5623958333</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2232" t="n">
         <v>33</v>
@@ -60573,6 +60573,32 @@
         <v>362</v>
       </c>
       <c r="H2232" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" s="1" t="n">
+        <v>45982.6095601852</v>
+      </c>
+      <c r="B2233" t="n">
+        <v>217</v>
+      </c>
+      <c r="C2233" t="n">
+        <v>290</v>
+      </c>
+      <c r="D2233" t="n">
+        <v>288</v>
+      </c>
+      <c r="E2233" t="n">
+        <v>289</v>
+      </c>
+      <c r="F2233" t="n">
+        <v>290</v>
+      </c>
+      <c r="G2233" t="s">
+        <v>362</v>
+      </c>
+      <c r="H2233" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398651123047</t>
+    <t xml:space="preserve">358.398681640625</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622741699219</t>
+    <t xml:space="preserve">334.139007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
     <t xml:space="preserve">338.119079589844</t>
@@ -83,73 +83,73 @@
     <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
-    <t xml:space="preserve">330.727478027344</t>
+    <t xml:space="preserve">330.727447509766</t>
   </si>
   <si>
     <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">343.804931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.438446044922</t>
+    <t xml:space="preserve">343.804962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.4384765625</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">338.30859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046813964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">343.046844482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071960449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391296386719</t>
+    <t xml:space="preserve">357.071929931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391326904297</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077178955078</t>
+    <t xml:space="preserve">375.077209472656</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">371.476135253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">361.620666503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
+    <t xml:space="preserve">371.476165771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">361.620635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
   </si>
   <si>
     <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
@@ -60578,7 +60578,7 @@
     </row>
     <row r="2233">
       <c r="A2233" s="1" t="n">
-        <v>45982.6095601852</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2233" t="n">
         <v>217</v>
@@ -60599,6 +60599,32 @@
         <v>362</v>
       </c>
       <c r="H2233" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" s="1" t="n">
+        <v>45985.4551967593</v>
+      </c>
+      <c r="B2234" t="n">
+        <v>34</v>
+      </c>
+      <c r="C2234" t="n">
+        <v>289</v>
+      </c>
+      <c r="D2234" t="n">
+        <v>289</v>
+      </c>
+      <c r="E2234" t="n">
+        <v>289</v>
+      </c>
+      <c r="F2234" t="n">
+        <v>289</v>
+      </c>
+      <c r="G2234" t="s">
+        <v>730</v>
+      </c>
+      <c r="H2234" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398681640625</t>
+    <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099182128906</t>
+    <t xml:space="preserve">342.099212646484</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
@@ -74,31 +74,31 @@
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727447509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.804962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.4384765625</t>
+    <t xml:space="preserve">338.119110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366241455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.804931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.438415527344</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
+    <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -107,61 +107,61 @@
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046844482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785064697266</t>
+    <t xml:space="preserve">343.046813964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528503417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.071929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.939971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077209472656</t>
+    <t xml:space="preserve">370.528533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.071960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.940002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">371.476165771484</t>
+    <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496032714844</t>
+    <t xml:space="preserve">367.496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -60604,7 +60604,7 @@
     </row>
     <row r="2234">
       <c r="A2234" s="1" t="n">
-        <v>45985.4551967593</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2234" t="n">
         <v>34</v>
@@ -60625,6 +60625,32 @@
         <v>730</v>
       </c>
       <c r="H2234" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" s="1" t="n">
+        <v>45986.6747222222</v>
+      </c>
+      <c r="B2235" t="n">
+        <v>139</v>
+      </c>
+      <c r="C2235" t="n">
+        <v>290</v>
+      </c>
+      <c r="D2235" t="n">
+        <v>289</v>
+      </c>
+      <c r="E2235" t="n">
+        <v>290</v>
+      </c>
+      <c r="F2235" t="n">
+        <v>289</v>
+      </c>
+      <c r="G2235" t="s">
+        <v>730</v>
+      </c>
+      <c r="H2235" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">360.104431152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -59,46 +59,46 @@
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.700225830078</t>
+    <t xml:space="preserve">345.7001953125</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099212646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.139007568359</t>
+    <t xml:space="preserve">342.099182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.138977050781</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119110107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366241455078</t>
+    <t xml:space="preserve">338.119079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438415527344</t>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
+    <t xml:space="preserve">338.30859375</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.071960449219</t>
+    <t xml:space="preserve">370.528503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077178955078</t>
+    <t xml:space="preserve">375.077209472656</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
@@ -140,22 +140,22 @@
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496002197266</t>
+    <t xml:space="preserve">367.496032714844</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
@@ -60630,7 +60630,7 @@
     </row>
     <row r="2235">
       <c r="A2235" s="1" t="n">
-        <v>45986.6747222222</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2235" t="n">
         <v>139</v>
@@ -60651,6 +60651,32 @@
         <v>730</v>
       </c>
       <c r="H2235" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" s="1" t="n">
+        <v>45987.610474537</v>
+      </c>
+      <c r="B2236" t="n">
+        <v>195</v>
+      </c>
+      <c r="C2236" t="n">
+        <v>290</v>
+      </c>
+      <c r="D2236" t="n">
+        <v>289</v>
+      </c>
+      <c r="E2236" t="n">
+        <v>289</v>
+      </c>
+      <c r="F2236" t="n">
+        <v>290</v>
+      </c>
+      <c r="G2236" t="s">
+        <v>362</v>
+      </c>
+      <c r="H2236" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104431152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">360.104400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -59,46 +59,46 @@
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.7001953125</t>
+    <t xml:space="preserve">345.700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.138977050781</t>
+    <t xml:space="preserve">342.099212646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">338.119110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366241455078</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438446044922</t>
+    <t xml:space="preserve">350.438415527344</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
+    <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528503417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.071929931641</t>
+    <t xml:space="preserve">370.528533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077209472656</t>
+    <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
@@ -140,22 +140,22 @@
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496032714844</t>
+    <t xml:space="preserve">367.496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
@@ -60656,7 +60656,7 @@
     </row>
     <row r="2236">
       <c r="A2236" s="1" t="n">
-        <v>45987.610474537</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2236" t="n">
         <v>195</v>
@@ -60677,6 +60677,32 @@
         <v>362</v>
       </c>
       <c r="H2236" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" s="1" t="n">
+        <v>45988.3807638889</v>
+      </c>
+      <c r="B2237" t="n">
+        <v>59</v>
+      </c>
+      <c r="C2237" t="n">
+        <v>289</v>
+      </c>
+      <c r="D2237" t="n">
+        <v>289</v>
+      </c>
+      <c r="E2237" t="n">
+        <v>289</v>
+      </c>
+      <c r="F2237" t="n">
+        <v>289</v>
+      </c>
+      <c r="G2237" t="s">
+        <v>730</v>
+      </c>
+      <c r="H2237" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398651123047</t>
+    <t xml:space="preserve">358.398681640625</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099212646484</t>
+    <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
@@ -74,31 +74,31 @@
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119110107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366241455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.804931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.438415527344</t>
+    <t xml:space="preserve">338.119079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727447509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.804962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.4384765625</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
+    <t xml:space="preserve">338.30859375</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -107,61 +107,61 @@
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046813964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785034179688</t>
+    <t xml:space="preserve">343.046844482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785064697266</t>
   </si>
   <si>
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.071960449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.940002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077178955078</t>
+    <t xml:space="preserve">370.528503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.071929931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.939971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077209472656</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">371.476135253906</t>
+    <t xml:space="preserve">371.476165771484</t>
   </si>
   <si>
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496002197266</t>
+    <t xml:space="preserve">367.496032714844</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -60682,7 +60682,7 @@
     </row>
     <row r="2237">
       <c r="A2237" s="1" t="n">
-        <v>45988.3807638889</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2237" t="n">
         <v>59</v>
@@ -60703,6 +60703,32 @@
         <v>730</v>
       </c>
       <c r="H2237" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" s="1" t="n">
+        <v>45989.677037037</v>
+      </c>
+      <c r="B2238" t="n">
+        <v>127</v>
+      </c>
+      <c r="C2238" t="n">
+        <v>289</v>
+      </c>
+      <c r="D2238" t="n">
+        <v>287</v>
+      </c>
+      <c r="E2238" t="n">
+        <v>287</v>
+      </c>
+      <c r="F2238" t="n">
+        <v>288</v>
+      </c>
+      <c r="G2238" t="s">
+        <v>729</v>
+      </c>
+      <c r="H2238" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398681640625</t>
+    <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622772216797</t>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622741699219</t>
   </si>
   <si>
     <t xml:space="preserve">338.119079589844</t>
@@ -83,73 +83,73 @@
     <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
-    <t xml:space="preserve">330.727447509766</t>
+    <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
     <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">343.804962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.4384765625</t>
+    <t xml:space="preserve">343.804931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">338.308624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046844482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785064697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">343.046813964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391326904297</t>
+    <t xml:space="preserve">357.071960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077209472656</t>
+    <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">371.476165771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">361.620635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
+    <t xml:space="preserve">371.476135253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">361.620666503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
     <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">362.947326660156</t>
+    <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
@@ -60708,7 +60708,7 @@
     </row>
     <row r="2238">
       <c r="A2238" s="1" t="n">
-        <v>45989.677037037</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2238" t="n">
         <v>127</v>
@@ -60729,6 +60729,32 @@
         <v>729</v>
       </c>
       <c r="H2238" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" s="1" t="n">
+        <v>45992.6656944444</v>
+      </c>
+      <c r="B2239" t="n">
+        <v>207</v>
+      </c>
+      <c r="C2239" t="n">
+        <v>289</v>
+      </c>
+      <c r="D2239" t="n">
+        <v>286</v>
+      </c>
+      <c r="E2239" t="n">
+        <v>289</v>
+      </c>
+      <c r="F2239" t="n">
+        <v>289</v>
+      </c>
+      <c r="G2239" t="s">
+        <v>730</v>
+      </c>
+      <c r="H2239" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -60734,7 +60734,7 @@
     </row>
     <row r="2239">
       <c r="A2239" s="1" t="n">
-        <v>45992.6656944444</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B2239" t="n">
         <v>207</v>
@@ -60755,6 +60755,32 @@
         <v>730</v>
       </c>
       <c r="H2239" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" s="1" t="n">
+        <v>45993.6545833333</v>
+      </c>
+      <c r="B2240" t="n">
+        <v>78</v>
+      </c>
+      <c r="C2240" t="n">
+        <v>288</v>
+      </c>
+      <c r="D2240" t="n">
+        <v>287</v>
+      </c>
+      <c r="E2240" t="n">
+        <v>287</v>
+      </c>
+      <c r="F2240" t="n">
+        <v>288</v>
+      </c>
+      <c r="G2240" t="s">
+        <v>729</v>
+      </c>
+      <c r="H2240" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104400634766</t>
+    <t xml:space="preserve">360.104431152344</t>
   </si>
   <si>
     <t xml:space="preserve">359.914916992188</t>
@@ -56,10 +56,10 @@
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.700225830078</t>
+    <t xml:space="preserve">339.824859619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.7001953125</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">334.138977050781</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622741699219</t>
+    <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
     <t xml:space="preserve">338.119079589844</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">338.30859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071960449219</t>
+    <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">373.939971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077178955078</t>
+    <t xml:space="preserve">373.940002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077209472656</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
@@ -137,19 +137,19 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620666503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
+    <t xml:space="preserve">361.620635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
   </si>
   <si>
     <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -60760,7 +60760,7 @@
     </row>
     <row r="2240">
       <c r="A2240" s="1" t="n">
-        <v>45993.6545833333</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2240" t="n">
         <v>78</v>
@@ -60781,6 +60781,32 @@
         <v>729</v>
       </c>
       <c r="H2240" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" s="1" t="n">
+        <v>45994.4077083333</v>
+      </c>
+      <c r="B2241" t="n">
+        <v>297</v>
+      </c>
+      <c r="C2241" t="n">
+        <v>290</v>
+      </c>
+      <c r="D2241" t="n">
+        <v>289</v>
+      </c>
+      <c r="E2241" t="n">
+        <v>289</v>
+      </c>
+      <c r="F2241" t="n">
+        <v>290</v>
+      </c>
+      <c r="G2241" t="s">
+        <v>362</v>
+      </c>
+      <c r="H2241" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104431152344</t>
+    <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.627990722656</t>
+    <t xml:space="preserve">350.628021240234</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.7001953125</t>
+    <t xml:space="preserve">345.700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
+    <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
+    <t xml:space="preserve">331.675170898438</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">355.366180419922</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">338.308624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,49 +110,49 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">347.785064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.940002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">357.071960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.939971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">361.620666503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313873291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -60786,7 +60786,7 @@
     </row>
     <row r="2241">
       <c r="A2241" s="1" t="n">
-        <v>45994.4077083333</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2241" t="n">
         <v>297</v>
@@ -60807,6 +60807,32 @@
         <v>362</v>
       </c>
       <c r="H2241" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" s="1" t="n">
+        <v>45995.6761921296</v>
+      </c>
+      <c r="B2242" t="n">
+        <v>207</v>
+      </c>
+      <c r="C2242" t="n">
+        <v>291</v>
+      </c>
+      <c r="D2242" t="n">
+        <v>290</v>
+      </c>
+      <c r="E2242" t="n">
+        <v>290</v>
+      </c>
+      <c r="F2242" t="n">
+        <v>290</v>
+      </c>
+      <c r="G2242" t="s">
+        <v>362</v>
+      </c>
+      <c r="H2242" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398651123047</t>
+    <t xml:space="preserve">358.398681640625</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.628021240234</t>
+    <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
@@ -74,52 +74,52 @@
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675170898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366180419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.804931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.438446044922</t>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727447509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.804962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.4384765625</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">338.30859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046813964844</t>
+    <t xml:space="preserve">343.046844482422</t>
   </si>
   <si>
     <t xml:space="preserve">347.785064697266</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071960449219</t>
+    <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">369.391326904297</t>
@@ -128,31 +128,31 @@
     <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">371.476135253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">361.620666503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313873291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">366.548431396484</t>
+    <t xml:space="preserve">375.077209472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">371.476165771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">361.620635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -60812,7 +60812,7 @@
     </row>
     <row r="2242">
       <c r="A2242" s="1" t="n">
-        <v>45995.6761921296</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B2242" t="n">
         <v>207</v>
@@ -60833,6 +60833,32 @@
         <v>362</v>
       </c>
       <c r="H2242" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" s="1" t="n">
+        <v>45996.687349537</v>
+      </c>
+      <c r="B2243" t="n">
+        <v>195</v>
+      </c>
+      <c r="C2243" t="n">
+        <v>292</v>
+      </c>
+      <c r="D2243" t="n">
+        <v>290</v>
+      </c>
+      <c r="E2243" t="n">
+        <v>291</v>
+      </c>
+      <c r="F2243" t="n">
+        <v>290</v>
+      </c>
+      <c r="G2243" t="s">
+        <v>362</v>
+      </c>
+      <c r="H2243" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398681640625</t>
+    <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622772216797</t>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622741699219</t>
   </si>
   <si>
     <t xml:space="preserve">338.119079589844</t>
@@ -83,73 +83,73 @@
     <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
-    <t xml:space="preserve">330.727447509766</t>
+    <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
     <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">343.804962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.4384765625</t>
+    <t xml:space="preserve">343.804931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">338.308624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046844482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785064697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">343.046813964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391326904297</t>
+    <t xml:space="preserve">357.071960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077209472656</t>
+    <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">371.476165771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">361.620635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
+    <t xml:space="preserve">371.476135253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">361.620666503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
     <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">362.947326660156</t>
+    <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
@@ -60838,7 +60838,7 @@
     </row>
     <row r="2243">
       <c r="A2243" s="1" t="n">
-        <v>45996.687349537</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B2243" t="n">
         <v>195</v>
@@ -60859,6 +60859,32 @@
         <v>362</v>
       </c>
       <c r="H2243" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" s="1" t="n">
+        <v>45999.6913078704</v>
+      </c>
+      <c r="B2244" t="n">
+        <v>1579</v>
+      </c>
+      <c r="C2244" t="n">
+        <v>297</v>
+      </c>
+      <c r="D2244" t="n">
+        <v>296</v>
+      </c>
+      <c r="E2244" t="n">
+        <v>296</v>
+      </c>
+      <c r="F2244" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2244" t="s">
+        <v>359</v>
+      </c>
+      <c r="H2244" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -65,34 +65,34 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.138977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">342.099212646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.139007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366241455078</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438446044922</t>
+    <t xml:space="preserve">350.438415527344</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580871582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">370.528503417969</t>
+    <t xml:space="preserve">369.580841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">370.528533935547</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">373.939971923828</t>
+    <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620666503906</t>
+    <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313842773438</t>
+    <t xml:space="preserve">356.313812255859</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
@@ -155,13 +155,13 @@
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496032714844</t>
+    <t xml:space="preserve">367.496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -60864,7 +60864,7 @@
     </row>
     <row r="2244">
       <c r="A2244" s="1" t="n">
-        <v>45999.6913078704</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B2244" t="n">
         <v>1579</v>
@@ -60885,6 +60885,32 @@
         <v>359</v>
       </c>
       <c r="H2244" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" s="1" t="n">
+        <v>46000.6700925926</v>
+      </c>
+      <c r="B2245" t="n">
+        <v>2750</v>
+      </c>
+      <c r="C2245" t="n">
+        <v>296</v>
+      </c>
+      <c r="D2245" t="n">
+        <v>295</v>
+      </c>
+      <c r="E2245" t="n">
+        <v>296</v>
+      </c>
+      <c r="F2245" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2245" t="s">
+        <v>359</v>
+      </c>
+      <c r="H2245" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -65,34 +65,34 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099212646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119110107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366241455078</t>
+    <t xml:space="preserve">342.099182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438415527344</t>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">370.528533935547</t>
+    <t xml:space="preserve">369.580871582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">373.940002441406</t>
+    <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
+    <t xml:space="preserve">361.620666503906</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313812255859</t>
+    <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
@@ -155,13 +155,13 @@
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496002197266</t>
+    <t xml:space="preserve">367.496032714844</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -60890,7 +60890,7 @@
     </row>
     <row r="2245">
       <c r="A2245" s="1" t="n">
-        <v>46000.6700925926</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2245" t="n">
         <v>2750</v>
@@ -60911,6 +60911,32 @@
         <v>359</v>
       </c>
       <c r="H2245" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" s="1" t="n">
+        <v>46001.516875</v>
+      </c>
+      <c r="B2246" t="n">
+        <v>435</v>
+      </c>
+      <c r="C2246" t="n">
+        <v>296</v>
+      </c>
+      <c r="D2246" t="n">
+        <v>296</v>
+      </c>
+      <c r="E2246" t="n">
+        <v>296</v>
+      </c>
+      <c r="F2246" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2246" t="s">
+        <v>359</v>
+      </c>
+      <c r="H2246" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -60916,7 +60916,7 @@
     </row>
     <row r="2246">
       <c r="A2246" s="1" t="n">
-        <v>46001.516875</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B2246" t="n">
         <v>435</v>
@@ -60937,6 +60937,32 @@
         <v>359</v>
       </c>
       <c r="H2246" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" s="1" t="n">
+        <v>46002.6571180556</v>
+      </c>
+      <c r="B2247" t="n">
+        <v>330</v>
+      </c>
+      <c r="C2247" t="n">
+        <v>296</v>
+      </c>
+      <c r="D2247" t="n">
+        <v>296</v>
+      </c>
+      <c r="E2247" t="n">
+        <v>296</v>
+      </c>
+      <c r="F2247" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2247" t="s">
+        <v>359</v>
+      </c>
+      <c r="H2247" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="733">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2208,6 +2208,9 @@
   </si>
   <si>
     <t xml:space="preserve">291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295</t>
   </si>
 </sst>
 </file>
@@ -60942,7 +60945,7 @@
     </row>
     <row r="2247">
       <c r="A2247" s="1" t="n">
-        <v>46002.6571180556</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B2247" t="n">
         <v>330</v>
@@ -60963,6 +60966,32 @@
         <v>359</v>
       </c>
       <c r="H2247" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" s="1" t="n">
+        <v>46003.6867476852</v>
+      </c>
+      <c r="B2248" t="n">
+        <v>818</v>
+      </c>
+      <c r="C2248" t="n">
+        <v>296</v>
+      </c>
+      <c r="D2248" t="n">
+        <v>295</v>
+      </c>
+      <c r="E2248" t="n">
+        <v>296</v>
+      </c>
+      <c r="F2248" t="n">
+        <v>295</v>
+      </c>
+      <c r="G2248" t="s">
+        <v>732</v>
+      </c>
+      <c r="H2248" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="734">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
+    <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
     <t xml:space="preserve">332.622741699219</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
+    <t xml:space="preserve">331.675109863281</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151550292969</t>
+    <t xml:space="preserve">341.151519775391</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
@@ -125,19 +125,19 @@
     <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">373.939971923828</t>
+    <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620666503906</t>
+    <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313842773438</t>
+    <t xml:space="preserve">356.313812255859</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -2211,6 +2211,9 @@
   </si>
   <si>
     <t xml:space="preserve">295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294</t>
   </si>
 </sst>
 </file>
@@ -60971,7 +60974,7 @@
     </row>
     <row r="2248">
       <c r="A2248" s="1" t="n">
-        <v>46003.6867476852</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B2248" t="n">
         <v>818</v>
@@ -60992,6 +60995,32 @@
         <v>732</v>
       </c>
       <c r="H2248" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" s="1" t="n">
+        <v>46006.4180787037</v>
+      </c>
+      <c r="B2249" t="n">
+        <v>411</v>
+      </c>
+      <c r="C2249" t="n">
+        <v>295</v>
+      </c>
+      <c r="D2249" t="n">
+        <v>294</v>
+      </c>
+      <c r="E2249" t="n">
+        <v>295</v>
+      </c>
+      <c r="F2249" t="n">
+        <v>294</v>
+      </c>
+      <c r="G2249" t="s">
+        <v>733</v>
+      </c>
+      <c r="H2249" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
+    <t xml:space="preserve">334.138977050781</t>
   </si>
   <si>
     <t xml:space="preserve">332.622741699219</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675109863281</t>
+    <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151519775391</t>
+    <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
@@ -125,19 +125,19 @@
     <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">373.940002441406</t>
+    <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
+    <t xml:space="preserve">361.620666503906</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313812255859</t>
+    <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -61000,7 +61000,7 @@
     </row>
     <row r="2249">
       <c r="A2249" s="1" t="n">
-        <v>46006.4180787037</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B2249" t="n">
         <v>411</v>
@@ -61021,6 +61021,32 @@
         <v>733</v>
       </c>
       <c r="H2249" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" s="1" t="n">
+        <v>46007.6433217593</v>
+      </c>
+      <c r="B2250" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C2250" t="n">
+        <v>295</v>
+      </c>
+      <c r="D2250" t="n">
+        <v>295</v>
+      </c>
+      <c r="E2250" t="n">
+        <v>295</v>
+      </c>
+      <c r="F2250" t="n">
+        <v>295</v>
+      </c>
+      <c r="G2250" t="s">
+        <v>732</v>
+      </c>
+      <c r="H2250" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -53,10 +53,10 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.627990722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">350.628021240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">334.139007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
+    <t xml:space="preserve">331.675170898438</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">355.366180419922</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785034179688</t>
+    <t xml:space="preserve">347.785064697266</t>
   </si>
   <si>
     <t xml:space="preserve">369.580871582031</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391296386719</t>
+    <t xml:space="preserve">369.391326904297</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313842773438</t>
+    <t xml:space="preserve">356.313873291016</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -61026,7 +61026,7 @@
     </row>
     <row r="2250">
       <c r="A2250" s="1" t="n">
-        <v>46007.6433217593</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B2250" t="n">
         <v>1250</v>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -61050,6 +61050,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2251">
+      <c r="A2251" s="1" t="n">
+        <v>46008.3333333333</v>
+      </c>
+      <c r="B2251" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2251" t="n">
+        <v>295</v>
+      </c>
+      <c r="D2251" t="n">
+        <v>295</v>
+      </c>
+      <c r="E2251" t="n">
+        <v>295</v>
+      </c>
+      <c r="F2251" t="n">
+        <v>295</v>
+      </c>
+      <c r="G2251" t="s">
+        <v>732</v>
+      </c>
+      <c r="H2251" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" s="1" t="n">
+        <v>46009.686724537</v>
+      </c>
+      <c r="B2252" t="n">
+        <v>417</v>
+      </c>
+      <c r="C2252" t="n">
+        <v>295</v>
+      </c>
+      <c r="D2252" t="n">
+        <v>295</v>
+      </c>
+      <c r="E2252" t="n">
+        <v>295</v>
+      </c>
+      <c r="F2252" t="n">
+        <v>295</v>
+      </c>
+      <c r="G2252" t="s">
+        <v>732</v>
+      </c>
+      <c r="H2252" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -53,10 +53,10 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.628021240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">350.627990722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675170898438</t>
+    <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.366180419922</t>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785064697266</t>
+    <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">369.580871582031</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391326904297</t>
+    <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313873291016</t>
+    <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548431396484</t>
+    <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -61078,7 +61078,7 @@
     </row>
     <row r="2252">
       <c r="A2252" s="1" t="n">
-        <v>46009.686724537</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B2252" t="n">
         <v>417</v>
@@ -61099,6 +61099,32 @@
         <v>732</v>
       </c>
       <c r="H2252" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" s="1" t="n">
+        <v>46010.6227777778</v>
+      </c>
+      <c r="B2253" t="n">
+        <v>38</v>
+      </c>
+      <c r="C2253" t="n">
+        <v>295</v>
+      </c>
+      <c r="D2253" t="n">
+        <v>295</v>
+      </c>
+      <c r="E2253" t="n">
+        <v>295</v>
+      </c>
+      <c r="F2253" t="n">
+        <v>295</v>
+      </c>
+      <c r="G2253" t="s">
+        <v>732</v>
+      </c>
+      <c r="H2253" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -61104,7 +61104,7 @@
     </row>
     <row r="2253">
       <c r="A2253" s="1" t="n">
-        <v>46010.6227777778</v>
+        <v>46010.3333333333</v>
       </c>
       <c r="B2253" t="n">
         <v>38</v>
@@ -61125,6 +61125,32 @@
         <v>732</v>
       </c>
       <c r="H2253" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" s="1" t="n">
+        <v>46013.6354513889</v>
+      </c>
+      <c r="B2254" t="n">
+        <v>58</v>
+      </c>
+      <c r="C2254" t="n">
+        <v>295</v>
+      </c>
+      <c r="D2254" t="n">
+        <v>295</v>
+      </c>
+      <c r="E2254" t="n">
+        <v>295</v>
+      </c>
+      <c r="F2254" t="n">
+        <v>295</v>
+      </c>
+      <c r="G2254" t="s">
+        <v>732</v>
+      </c>
+      <c r="H2254" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104400634766</t>
+    <t xml:space="preserve">360.104431152344</t>
   </si>
   <si>
     <t xml:space="preserve">359.914916992188</t>
@@ -56,10 +56,10 @@
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.700225830078</t>
+    <t xml:space="preserve">339.824859619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.7001953125</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">334.138977050781</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622741699219</t>
+    <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
     <t xml:space="preserve">338.119079589844</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">338.30859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071960449219</t>
+    <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">373.939971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077178955078</t>
+    <t xml:space="preserve">373.940002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077209472656</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
@@ -137,19 +137,19 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620666503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
+    <t xml:space="preserve">361.620635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
   </si>
   <si>
     <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -61130,7 +61130,7 @@
     </row>
     <row r="2254">
       <c r="A2254" s="1" t="n">
-        <v>46013.6354513889</v>
+        <v>46013.3333333333</v>
       </c>
       <c r="B2254" t="n">
         <v>58</v>
@@ -61151,6 +61151,32 @@
         <v>732</v>
       </c>
       <c r="H2254" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" s="1" t="n">
+        <v>46014.412650463</v>
+      </c>
+      <c r="B2255" t="n">
+        <v>559</v>
+      </c>
+      <c r="C2255" t="n">
+        <v>296</v>
+      </c>
+      <c r="D2255" t="n">
+        <v>295</v>
+      </c>
+      <c r="E2255" t="n">
+        <v>295</v>
+      </c>
+      <c r="F2255" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2255" t="s">
+        <v>359</v>
+      </c>
+      <c r="H2255" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104431152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">360.104400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824859619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.7001953125</t>
+    <t xml:space="preserve">339.824829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">334.139007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
+    <t xml:space="preserve">331.675109863281</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151550292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.30859375</t>
+    <t xml:space="preserve">341.151519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071929931641</t>
+    <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">375.077178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
@@ -61156,7 +61156,7 @@
     </row>
     <row r="2255">
       <c r="A2255" s="1" t="n">
-        <v>46014.412650463</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B2255" t="n">
         <v>559</v>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">360.104431152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.700225830078</t>
+    <t xml:space="preserve">339.824859619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.7001953125</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675109863281</t>
+    <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.308624267578</t>
+    <t xml:space="preserve">341.151550292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.30859375</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071960449219</t>
+    <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">375.077209472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104431152344</t>
+    <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.627990722656</t>
+    <t xml:space="preserve">350.628021240234</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.7001953125</t>
+    <t xml:space="preserve">345.700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
+    <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
+    <t xml:space="preserve">331.675170898438</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">355.366180419922</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">338.308624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,49 +110,49 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">347.785064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.940002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">357.071960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.939971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">361.620666503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313873291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -61180,6 +61180,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2256">
+      <c r="A2256" s="1" t="n">
+        <v>46020.5322337963</v>
+      </c>
+      <c r="B2256" t="n">
+        <v>214</v>
+      </c>
+      <c r="C2256" t="n">
+        <v>296</v>
+      </c>
+      <c r="D2256" t="n">
+        <v>295</v>
+      </c>
+      <c r="E2256" t="n">
+        <v>296</v>
+      </c>
+      <c r="F2256" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2256" t="s">
+        <v>359</v>
+      </c>
+      <c r="H2256" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -53,10 +53,10 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.628021240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">350.627990722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675170898438</t>
+    <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.366180419922</t>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785064697266</t>
+    <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">369.580871582031</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391326904297</t>
+    <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313873291016</t>
+    <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548431396484</t>
+    <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -61182,7 +61182,7 @@
     </row>
     <row r="2256">
       <c r="A2256" s="1" t="n">
-        <v>46020.5322337963</v>
+        <v>46020.3333333333</v>
       </c>
       <c r="B2256" t="n">
         <v>214</v>
@@ -61203,6 +61203,32 @@
         <v>359</v>
       </c>
       <c r="H2256" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" s="1" t="n">
+        <v>46021.683900463</v>
+      </c>
+      <c r="B2257" t="n">
+        <v>324</v>
+      </c>
+      <c r="C2257" t="n">
+        <v>296</v>
+      </c>
+      <c r="D2257" t="n">
+        <v>296</v>
+      </c>
+      <c r="E2257" t="n">
+        <v>296</v>
+      </c>
+      <c r="F2257" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2257" t="s">
+        <v>359</v>
+      </c>
+      <c r="H2257" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -53,10 +53,10 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.627990722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">350.628021240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">334.139007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
+    <t xml:space="preserve">331.675170898438</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">355.366180419922</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785034179688</t>
+    <t xml:space="preserve">347.785064697266</t>
   </si>
   <si>
     <t xml:space="preserve">369.580871582031</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391296386719</t>
+    <t xml:space="preserve">369.391326904297</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313842773438</t>
+    <t xml:space="preserve">356.313873291016</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -61208,7 +61208,7 @@
     </row>
     <row r="2257">
       <c r="A2257" s="1" t="n">
-        <v>46021.683900463</v>
+        <v>46021.3333333333</v>
       </c>
       <c r="B2257" t="n">
         <v>324</v>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398651123047</t>
+    <t xml:space="preserve">358.398681640625</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.628021240234</t>
+    <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
@@ -74,52 +74,52 @@
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675170898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366180419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.804931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.438446044922</t>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727447509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.804962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.4384765625</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">338.30859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046813964844</t>
+    <t xml:space="preserve">343.046844482422</t>
   </si>
   <si>
     <t xml:space="preserve">347.785064697266</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071960449219</t>
+    <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">369.391326904297</t>
@@ -128,31 +128,31 @@
     <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">371.476135253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">361.620666503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313873291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">366.548431396484</t>
+    <t xml:space="preserve">375.077209472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">371.476165771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">361.620635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398681640625</t>
+    <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099182128906</t>
+    <t xml:space="preserve">342.099212646484</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
@@ -74,31 +74,31 @@
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727447509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.804962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.4384765625</t>
+    <t xml:space="preserve">338.119110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366241455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.804931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.438415527344</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
+    <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -107,61 +107,61 @@
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046844482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785064697266</t>
+    <t xml:space="preserve">343.046813964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528503417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.071929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.939971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077209472656</t>
+    <t xml:space="preserve">370.528533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.071960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.940002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">371.476165771484</t>
+    <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496032714844</t>
+    <t xml:space="preserve">367.496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="735">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,10 +50,10 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.627990722656</t>
+    <t xml:space="preserve">359.914916992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.628021240234</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099212646484</t>
+    <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
@@ -77,22 +77,22 @@
     <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
-    <t xml:space="preserve">345.889801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366241455078</t>
+    <t xml:space="preserve">345.889770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366180419922</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438415527344</t>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,34 +110,34 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">370.528533935547</t>
+    <t xml:space="preserve">347.785064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580871582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.940002441406</t>
+    <t xml:space="preserve">369.391326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
+    <t xml:space="preserve">361.620666503906</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,22 +146,22 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313812255859</t>
+    <t xml:space="preserve">356.313873291016</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548400878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.496002197266</t>
+    <t xml:space="preserve">366.548431396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.496032714844</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -2214,6 +2214,9 @@
   </si>
   <si>
     <t xml:space="preserve">294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297</t>
   </si>
 </sst>
 </file>
@@ -61232,6 +61235,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2258">
+      <c r="A2258" s="1" t="n">
+        <v>46024.3333333333</v>
+      </c>
+      <c r="B2258" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2258" t="n">
+        <v>296</v>
+      </c>
+      <c r="D2258" t="n">
+        <v>296</v>
+      </c>
+      <c r="E2258" t="n">
+        <v>296</v>
+      </c>
+      <c r="F2258" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2258" t="s">
+        <v>359</v>
+      </c>
+      <c r="H2258" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" s="1" t="n">
+        <v>46027.5720833333</v>
+      </c>
+      <c r="B2259" t="n">
+        <v>264</v>
+      </c>
+      <c r="C2259" t="n">
+        <v>297</v>
+      </c>
+      <c r="D2259" t="n">
+        <v>296</v>
+      </c>
+      <c r="E2259" t="n">
+        <v>297</v>
+      </c>
+      <c r="F2259" t="n">
+        <v>297</v>
+      </c>
+      <c r="G2259" t="s">
+        <v>734</v>
+      </c>
+      <c r="H2259" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914916992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.628021240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">359.914886474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.627990722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622772216797</t>
+    <t xml:space="preserve">332.622741699219</t>
   </si>
   <si>
     <t xml:space="preserve">338.119110107422</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675170898438</t>
+    <t xml:space="preserve">331.675109863281</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.366180419922</t>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151550292969</t>
+    <t xml:space="preserve">341.151519775391</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785064697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">347.785034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.939971923828</t>
+    <t xml:space="preserve">369.391296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620666503906</t>
+    <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313873291016</t>
+    <t xml:space="preserve">356.313812255859</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548431396484</t>
+    <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -61263,7 +61263,7 @@
     </row>
     <row r="2259">
       <c r="A2259" s="1" t="n">
-        <v>46027.5720833333</v>
+        <v>46027.3333333333</v>
       </c>
       <c r="B2259" t="n">
         <v>264</v>
@@ -61284,6 +61284,32 @@
         <v>734</v>
       </c>
       <c r="H2259" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" s="1" t="n">
+        <v>46028.4868518518</v>
+      </c>
+      <c r="B2260" t="n">
+        <v>280</v>
+      </c>
+      <c r="C2260" t="n">
+        <v>297</v>
+      </c>
+      <c r="D2260" t="n">
+        <v>297</v>
+      </c>
+      <c r="E2260" t="n">
+        <v>297</v>
+      </c>
+      <c r="F2260" t="n">
+        <v>297</v>
+      </c>
+      <c r="G2260" t="s">
+        <v>734</v>
+      </c>
+      <c r="H2260" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -56,7 +56,7 @@
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -65,37 +65,37 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099182128906</t>
+    <t xml:space="preserve">342.099212646484</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622741699219</t>
+    <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
     <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
-    <t xml:space="preserve">345.889770507812</t>
+    <t xml:space="preserve">345.889801025391</t>
   </si>
   <si>
     <t xml:space="preserve">331.675109863281</t>
   </si>
   <si>
-    <t xml:space="preserve">330.727478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">330.727508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366241455078</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.151519775391</t>
+    <t xml:space="preserve">350.438415527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528503417969</t>
+    <t xml:space="preserve">370.528533935547</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496032714844</t>
+    <t xml:space="preserve">367.496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
@@ -61289,7 +61289,7 @@
     </row>
     <row r="2260">
       <c r="A2260" s="1" t="n">
-        <v>46028.4868518518</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B2260" t="n">
         <v>280</v>
@@ -61310,6 +61310,32 @@
         <v>734</v>
       </c>
       <c r="H2260" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" s="1" t="n">
+        <v>46029.6535648148</v>
+      </c>
+      <c r="B2261" t="n">
+        <v>235</v>
+      </c>
+      <c r="C2261" t="n">
+        <v>297</v>
+      </c>
+      <c r="D2261" t="n">
+        <v>297</v>
+      </c>
+      <c r="E2261" t="n">
+        <v>297</v>
+      </c>
+      <c r="F2261" t="n">
+        <v>297</v>
+      </c>
+      <c r="G2261" t="s">
+        <v>734</v>
+      </c>
+      <c r="H2261" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -61315,7 +61315,7 @@
     </row>
     <row r="2261">
       <c r="A2261" s="1" t="n">
-        <v>46029.6535648148</v>
+        <v>46029.3333333333</v>
       </c>
       <c r="B2261" t="n">
         <v>235</v>
@@ -61336,6 +61336,32 @@
         <v>734</v>
       </c>
       <c r="H2261" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="A2262" s="1" t="n">
+        <v>46030.6656597222</v>
+      </c>
+      <c r="B2262" t="n">
+        <v>62</v>
+      </c>
+      <c r="C2262" t="n">
+        <v>298</v>
+      </c>
+      <c r="D2262" t="n">
+        <v>297</v>
+      </c>
+      <c r="E2262" t="n">
+        <v>297</v>
+      </c>
+      <c r="F2262" t="n">
+        <v>297</v>
+      </c>
+      <c r="G2262" t="s">
+        <v>734</v>
+      </c>
+      <c r="H2262" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398651123047</t>
+    <t xml:space="preserve">358.398681640625</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099212646484</t>
+    <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
@@ -74,31 +74,31 @@
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119110107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366241455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.804931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.438415527344</t>
+    <t xml:space="preserve">338.119079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727447509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.804962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.4384765625</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
+    <t xml:space="preserve">338.30859375</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -107,61 +107,61 @@
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046813964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785034179688</t>
+    <t xml:space="preserve">343.046844482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785064697266</t>
   </si>
   <si>
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.071960449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.940002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077178955078</t>
+    <t xml:space="preserve">370.528503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.071929931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.939971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077209472656</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">371.476135253906</t>
+    <t xml:space="preserve">371.476165771484</t>
   </si>
   <si>
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496002197266</t>
+    <t xml:space="preserve">367.496032714844</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -61341,7 +61341,7 @@
     </row>
     <row r="2262">
       <c r="A2262" s="1" t="n">
-        <v>46030.6656597222</v>
+        <v>46030.3333333333</v>
       </c>
       <c r="B2262" t="n">
         <v>62</v>
@@ -61362,6 +61362,32 @@
         <v>734</v>
       </c>
       <c r="H2262" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" s="1" t="n">
+        <v>46031.687349537</v>
+      </c>
+      <c r="B2263" t="n">
+        <v>868</v>
+      </c>
+      <c r="C2263" t="n">
+        <v>297</v>
+      </c>
+      <c r="D2263" t="n">
+        <v>296</v>
+      </c>
+      <c r="E2263" t="n">
+        <v>297</v>
+      </c>
+      <c r="F2263" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2263" t="s">
+        <v>359</v>
+      </c>
+      <c r="H2263" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -61367,7 +61367,7 @@
     </row>
     <row r="2263">
       <c r="A2263" s="1" t="n">
-        <v>46031.687349537</v>
+        <v>46031.3333333333</v>
       </c>
       <c r="B2263" t="n">
         <v>868</v>
@@ -61388,6 +61388,32 @@
         <v>359</v>
       </c>
       <c r="H2263" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" s="1" t="n">
+        <v>46034.6705092593</v>
+      </c>
+      <c r="B2264" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2264" t="n">
+        <v>296</v>
+      </c>
+      <c r="D2264" t="n">
+        <v>296</v>
+      </c>
+      <c r="E2264" t="n">
+        <v>296</v>
+      </c>
+      <c r="F2264" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2264" t="s">
+        <v>359</v>
+      </c>
+      <c r="H2264" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398681640625</t>
+    <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622772216797</t>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622741699219</t>
   </si>
   <si>
     <t xml:space="preserve">338.119079589844</t>
@@ -83,73 +83,73 @@
     <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
-    <t xml:space="preserve">330.727447509766</t>
+    <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
     <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">343.804962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.4384765625</t>
+    <t xml:space="preserve">343.804931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">338.308624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046844482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785064697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">343.046813964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391326904297</t>
+    <t xml:space="preserve">357.071960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077209472656</t>
+    <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">371.476165771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">361.620635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
+    <t xml:space="preserve">371.476135253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">361.620666503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
     <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">362.947326660156</t>
+    <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
@@ -61393,7 +61393,7 @@
     </row>
     <row r="2264">
       <c r="A2264" s="1" t="n">
-        <v>46034.6705092593</v>
+        <v>46034.3333333333</v>
       </c>
       <c r="B2264" t="n">
         <v>18</v>
@@ -61414,6 +61414,32 @@
         <v>359</v>
       </c>
       <c r="H2264" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" s="1" t="n">
+        <v>46035.6066203704</v>
+      </c>
+      <c r="B2265" t="n">
+        <v>11</v>
+      </c>
+      <c r="C2265" t="n">
+        <v>296</v>
+      </c>
+      <c r="D2265" t="n">
+        <v>296</v>
+      </c>
+      <c r="E2265" t="n">
+        <v>296</v>
+      </c>
+      <c r="F2265" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2265" t="s">
+        <v>359</v>
+      </c>
+      <c r="H2265" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -53,10 +53,10 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.627990722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">350.628021240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">334.139007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
+    <t xml:space="preserve">331.675170898438</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">355.366180419922</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785034179688</t>
+    <t xml:space="preserve">347.785064697266</t>
   </si>
   <si>
     <t xml:space="preserve">369.580871582031</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391296386719</t>
+    <t xml:space="preserve">369.391326904297</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313842773438</t>
+    <t xml:space="preserve">356.313873291016</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -61419,7 +61419,7 @@
     </row>
     <row r="2265">
       <c r="A2265" s="1" t="n">
-        <v>46035.6066203704</v>
+        <v>46035.3333333333</v>
       </c>
       <c r="B2265" t="n">
         <v>11</v>
@@ -61440,6 +61440,32 @@
         <v>359</v>
       </c>
       <c r="H2265" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="A2266" s="1" t="n">
+        <v>46036.6845138889</v>
+      </c>
+      <c r="B2266" t="n">
+        <v>807</v>
+      </c>
+      <c r="C2266" t="n">
+        <v>297</v>
+      </c>
+      <c r="D2266" t="n">
+        <v>296</v>
+      </c>
+      <c r="E2266" t="n">
+        <v>297</v>
+      </c>
+      <c r="F2266" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2266" t="s">
+        <v>359</v>
+      </c>
+      <c r="H2266" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -61445,7 +61445,7 @@
     </row>
     <row r="2266">
       <c r="A2266" s="1" t="n">
-        <v>46036.6845138889</v>
+        <v>46036.3333333333</v>
       </c>
       <c r="B2266" t="n">
         <v>807</v>
@@ -61466,6 +61466,32 @@
         <v>359</v>
       </c>
       <c r="H2266" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" s="1" t="n">
+        <v>46037.6855555556</v>
+      </c>
+      <c r="B2267" t="n">
+        <v>355</v>
+      </c>
+      <c r="C2267" t="n">
+        <v>297</v>
+      </c>
+      <c r="D2267" t="n">
+        <v>296</v>
+      </c>
+      <c r="E2267" t="n">
+        <v>297</v>
+      </c>
+      <c r="F2267" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2267" t="s">
+        <v>359</v>
+      </c>
+      <c r="H2267" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -53,10 +53,10 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.628021240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">350.627990722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675170898438</t>
+    <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.366180419922</t>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785064697266</t>
+    <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">369.580871582031</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391326904297</t>
+    <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313873291016</t>
+    <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548431396484</t>
+    <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -61471,7 +61471,7 @@
     </row>
     <row r="2267">
       <c r="A2267" s="1" t="n">
-        <v>46037.6855555556</v>
+        <v>46037.3333333333</v>
       </c>
       <c r="B2267" t="n">
         <v>355</v>
@@ -61492,6 +61492,32 @@
         <v>359</v>
       </c>
       <c r="H2267" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" s="1" t="n">
+        <v>46038.6681134259</v>
+      </c>
+      <c r="B2268" t="n">
+        <v>205</v>
+      </c>
+      <c r="C2268" t="n">
+        <v>298</v>
+      </c>
+      <c r="D2268" t="n">
+        <v>297</v>
+      </c>
+      <c r="E2268" t="n">
+        <v>297</v>
+      </c>
+      <c r="F2268" t="n">
+        <v>297</v>
+      </c>
+      <c r="G2268" t="s">
+        <v>734</v>
+      </c>
+      <c r="H2268" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -65,34 +65,34 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.138977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">342.099212646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.139007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366241455078</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438446044922</t>
+    <t xml:space="preserve">350.438415527344</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580871582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">370.528503417969</t>
+    <t xml:space="preserve">369.580841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">370.528533935547</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">373.939971923828</t>
+    <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620666503906</t>
+    <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313842773438</t>
+    <t xml:space="preserve">356.313812255859</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
@@ -155,13 +155,13 @@
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496032714844</t>
+    <t xml:space="preserve">367.496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -61497,7 +61497,7 @@
     </row>
     <row r="2268">
       <c r="A2268" s="1" t="n">
-        <v>46038.6681134259</v>
+        <v>46038.3333333333</v>
       </c>
       <c r="B2268" t="n">
         <v>205</v>
@@ -61518,6 +61518,32 @@
         <v>734</v>
       </c>
       <c r="H2268" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" s="1" t="n">
+        <v>46041.6368171296</v>
+      </c>
+      <c r="B2269" t="n">
+        <v>260</v>
+      </c>
+      <c r="C2269" t="n">
+        <v>297</v>
+      </c>
+      <c r="D2269" t="n">
+        <v>296</v>
+      </c>
+      <c r="E2269" t="n">
+        <v>297</v>
+      </c>
+      <c r="F2269" t="n">
+        <v>297</v>
+      </c>
+      <c r="G2269" t="s">
+        <v>734</v>
+      </c>
+      <c r="H2269" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -61523,7 +61523,7 @@
     </row>
     <row r="2269">
       <c r="A2269" s="1" t="n">
-        <v>46041.6368171296</v>
+        <v>46041.3333333333</v>
       </c>
       <c r="B2269" t="n">
         <v>260</v>
@@ -61544,6 +61544,32 @@
         <v>734</v>
       </c>
       <c r="H2269" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" s="1" t="n">
+        <v>46042.6284375</v>
+      </c>
+      <c r="B2270" t="n">
+        <v>20</v>
+      </c>
+      <c r="C2270" t="n">
+        <v>297</v>
+      </c>
+      <c r="D2270" t="n">
+        <v>297</v>
+      </c>
+      <c r="E2270" t="n">
+        <v>297</v>
+      </c>
+      <c r="F2270" t="n">
+        <v>297</v>
+      </c>
+      <c r="G2270" t="s">
+        <v>734</v>
+      </c>
+      <c r="H2270" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -65,34 +65,34 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099212646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119110107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366241455078</t>
+    <t xml:space="preserve">342.099182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438415527344</t>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">370.528533935547</t>
+    <t xml:space="preserve">369.580871582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">373.940002441406</t>
+    <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
+    <t xml:space="preserve">361.620666503906</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313812255859</t>
+    <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
@@ -155,13 +155,13 @@
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496002197266</t>
+    <t xml:space="preserve">367.496032714844</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -61549,7 +61549,7 @@
     </row>
     <row r="2270">
       <c r="A2270" s="1" t="n">
-        <v>46042.6284375</v>
+        <v>46042.3333333333</v>
       </c>
       <c r="B2270" t="n">
         <v>20</v>
@@ -61570,6 +61570,32 @@
         <v>734</v>
       </c>
       <c r="H2270" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" s="1" t="n">
+        <v>46043.6741782407</v>
+      </c>
+      <c r="B2271" t="n">
+        <v>11</v>
+      </c>
+      <c r="C2271" t="n">
+        <v>297</v>
+      </c>
+      <c r="D2271" t="n">
+        <v>296</v>
+      </c>
+      <c r="E2271" t="n">
+        <v>296</v>
+      </c>
+      <c r="F2271" t="n">
+        <v>297</v>
+      </c>
+      <c r="G2271" t="s">
+        <v>734</v>
+      </c>
+      <c r="H2271" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -53,10 +53,10 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.627990722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">350.628021240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">334.139007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
+    <t xml:space="preserve">331.675170898438</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">355.366180419922</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785034179688</t>
+    <t xml:space="preserve">347.785064697266</t>
   </si>
   <si>
     <t xml:space="preserve">369.580871582031</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391296386719</t>
+    <t xml:space="preserve">369.391326904297</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313842773438</t>
+    <t xml:space="preserve">356.313873291016</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -61575,7 +61575,7 @@
     </row>
     <row r="2271">
       <c r="A2271" s="1" t="n">
-        <v>46043.6741782407</v>
+        <v>46043.3333333333</v>
       </c>
       <c r="B2271" t="n">
         <v>11</v>
@@ -61596,6 +61596,32 @@
         <v>734</v>
       </c>
       <c r="H2271" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" s="1" t="n">
+        <v>46044.3435532407</v>
+      </c>
+      <c r="B2272" t="n">
+        <v>80</v>
+      </c>
+      <c r="C2272" t="n">
+        <v>297</v>
+      </c>
+      <c r="D2272" t="n">
+        <v>297</v>
+      </c>
+      <c r="E2272" t="n">
+        <v>297</v>
+      </c>
+      <c r="F2272" t="n">
+        <v>297</v>
+      </c>
+      <c r="G2272" t="s">
+        <v>734</v>
+      </c>
+      <c r="H2272" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398651123047</t>
+    <t xml:space="preserve">358.398681640625</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.628021240234</t>
+    <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
@@ -74,52 +74,52 @@
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675170898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366180419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.804931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.438446044922</t>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727447509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.804962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.4384765625</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">338.30859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046813964844</t>
+    <t xml:space="preserve">343.046844482422</t>
   </si>
   <si>
     <t xml:space="preserve">347.785064697266</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071960449219</t>
+    <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">369.391326904297</t>
@@ -128,31 +128,31 @@
     <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">371.476135253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">361.620666503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313873291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">366.548431396484</t>
+    <t xml:space="preserve">375.077209472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">371.476165771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">361.620635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -61601,7 +61601,7 @@
     </row>
     <row r="2272">
       <c r="A2272" s="1" t="n">
-        <v>46044.3435532407</v>
+        <v>46044.3333333333</v>
       </c>
       <c r="B2272" t="n">
         <v>80</v>
@@ -61622,6 +61622,32 @@
         <v>734</v>
       </c>
       <c r="H2272" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" s="1" t="n">
+        <v>46045.5814236111</v>
+      </c>
+      <c r="B2273" t="n">
+        <v>215</v>
+      </c>
+      <c r="C2273" t="n">
+        <v>297</v>
+      </c>
+      <c r="D2273" t="n">
+        <v>297</v>
+      </c>
+      <c r="E2273" t="n">
+        <v>297</v>
+      </c>
+      <c r="F2273" t="n">
+        <v>297</v>
+      </c>
+      <c r="G2273" t="s">
+        <v>734</v>
+      </c>
+      <c r="H2273" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398681640625</t>
+    <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.627990722656</t>
+    <t xml:space="preserve">350.628021240234</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
@@ -74,52 +74,52 @@
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727447509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.804962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.4384765625</t>
+    <t xml:space="preserve">331.675170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366180419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.804931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">338.308624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046844482422</t>
+    <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
     <t xml:space="preserve">347.785064697266</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071929931641</t>
+    <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
     <t xml:space="preserve">369.391326904297</t>
@@ -128,31 +128,31 @@
     <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875122070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">371.476165771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">361.620635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">375.077178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875091552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">371.476135253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">361.620666503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313873291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -61627,7 +61627,7 @@
     </row>
     <row r="2273">
       <c r="A2273" s="1" t="n">
-        <v>46045.5814236111</v>
+        <v>46045.3333333333</v>
       </c>
       <c r="B2273" t="n">
         <v>215</v>
@@ -61648,6 +61648,32 @@
         <v>734</v>
       </c>
       <c r="H2273" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" s="1" t="n">
+        <v>46048.6554976852</v>
+      </c>
+      <c r="B2274" t="n">
+        <v>101</v>
+      </c>
+      <c r="C2274" t="n">
+        <v>296</v>
+      </c>
+      <c r="D2274" t="n">
+        <v>296</v>
+      </c>
+      <c r="E2274" t="n">
+        <v>296</v>
+      </c>
+      <c r="F2274" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2274" t="s">
+        <v>359</v>
+      </c>
+      <c r="H2274" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -53,10 +53,10 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.628021240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">350.627990722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675170898438</t>
+    <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.366180419922</t>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785064697266</t>
+    <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">369.580871582031</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391326904297</t>
+    <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313873291016</t>
+    <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548431396484</t>
+    <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -61653,7 +61653,7 @@
     </row>
     <row r="2274">
       <c r="A2274" s="1" t="n">
-        <v>46048.6554976852</v>
+        <v>46048.3333333333</v>
       </c>
       <c r="B2274" t="n">
         <v>101</v>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -65,34 +65,34 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.138977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">342.099212646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.139007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366241455078</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438446044922</t>
+    <t xml:space="preserve">350.438415527344</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580871582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">370.528503417969</t>
+    <t xml:space="preserve">369.580841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">370.528533935547</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">373.939971923828</t>
+    <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620666503906</t>
+    <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313842773438</t>
+    <t xml:space="preserve">356.313812255859</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
@@ -155,13 +155,13 @@
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496032714844</t>
+    <t xml:space="preserve">367.496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -61677,6 +61677,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2275">
+      <c r="A2275" s="1" t="n">
+        <v>46049.3333333333</v>
+      </c>
+      <c r="B2275" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2275" t="n">
+        <v>296</v>
+      </c>
+      <c r="D2275" t="n">
+        <v>296</v>
+      </c>
+      <c r="E2275" t="n">
+        <v>296</v>
+      </c>
+      <c r="F2275" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2275" t="s">
+        <v>359</v>
+      </c>
+      <c r="H2275" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" s="1" t="n">
+        <v>46050.6550115741</v>
+      </c>
+      <c r="B2276" t="n">
+        <v>139</v>
+      </c>
+      <c r="C2276" t="n">
+        <v>297</v>
+      </c>
+      <c r="D2276" t="n">
+        <v>297</v>
+      </c>
+      <c r="E2276" t="n">
+        <v>297</v>
+      </c>
+      <c r="F2276" t="n">
+        <v>297</v>
+      </c>
+      <c r="G2276" t="s">
+        <v>734</v>
+      </c>
+      <c r="H2276" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -56,7 +56,7 @@
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -65,37 +65,37 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099212646484</t>
+    <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622772216797</t>
+    <t xml:space="preserve">332.622741699219</t>
   </si>
   <si>
     <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
-    <t xml:space="preserve">345.889801025391</t>
+    <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
     <t xml:space="preserve">331.675109863281</t>
   </si>
   <si>
-    <t xml:space="preserve">330.727508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366241455078</t>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438415527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.151550292969</t>
+    <t xml:space="preserve">350.438446044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.151519775391</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528533935547</t>
+    <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496002197266</t>
+    <t xml:space="preserve">367.496032714844</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
@@ -61705,7 +61705,7 @@
     </row>
     <row r="2276">
       <c r="A2276" s="1" t="n">
-        <v>46050.6550115741</v>
+        <v>46050.3333333333</v>
       </c>
       <c r="B2276" t="n">
         <v>139</v>
@@ -61726,6 +61726,32 @@
         <v>734</v>
       </c>
       <c r="H2276" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" s="1" t="n">
+        <v>46051.6924074074</v>
+      </c>
+      <c r="B2277" t="n">
+        <v>365</v>
+      </c>
+      <c r="C2277" t="n">
+        <v>297</v>
+      </c>
+      <c r="D2277" t="n">
+        <v>297</v>
+      </c>
+      <c r="E2277" t="n">
+        <v>297</v>
+      </c>
+      <c r="F2277" t="n">
+        <v>297</v>
+      </c>
+      <c r="G2277" t="s">
+        <v>734</v>
+      </c>
+      <c r="H2277" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -56,7 +56,7 @@
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -65,37 +65,37 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099182128906</t>
+    <t xml:space="preserve">342.099212646484</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622741699219</t>
+    <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
     <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
-    <t xml:space="preserve">345.889770507812</t>
+    <t xml:space="preserve">345.889801025391</t>
   </si>
   <si>
     <t xml:space="preserve">331.675109863281</t>
   </si>
   <si>
-    <t xml:space="preserve">330.727478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">330.727508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366241455078</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.151519775391</t>
+    <t xml:space="preserve">350.438415527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528503417969</t>
+    <t xml:space="preserve">370.528533935547</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496032714844</t>
+    <t xml:space="preserve">367.496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
@@ -61731,7 +61731,7 @@
     </row>
     <row r="2277">
       <c r="A2277" s="1" t="n">
-        <v>46051.6924074074</v>
+        <v>46051.3333333333</v>
       </c>
       <c r="B2277" t="n">
         <v>365</v>
@@ -61752,6 +61752,32 @@
         <v>734</v>
       </c>
       <c r="H2277" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" s="1" t="n">
+        <v>46052.4675694444</v>
+      </c>
+      <c r="B2278" t="n">
+        <v>163</v>
+      </c>
+      <c r="C2278" t="n">
+        <v>297</v>
+      </c>
+      <c r="D2278" t="n">
+        <v>297</v>
+      </c>
+      <c r="E2278" t="n">
+        <v>297</v>
+      </c>
+      <c r="F2278" t="n">
+        <v>297</v>
+      </c>
+      <c r="G2278" t="s">
+        <v>734</v>
+      </c>
+      <c r="H2278" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">360.104431152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -59,46 +59,46 @@
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.700225830078</t>
+    <t xml:space="preserve">345.7001953125</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099212646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.139007568359</t>
+    <t xml:space="preserve">342.099182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.138977050781</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119110107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366241455078</t>
+    <t xml:space="preserve">338.119079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438415527344</t>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
+    <t xml:space="preserve">338.30859375</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.071960449219</t>
+    <t xml:space="preserve">370.528503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077178955078</t>
+    <t xml:space="preserve">375.077209472656</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
@@ -140,22 +140,22 @@
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496002197266</t>
+    <t xml:space="preserve">367.496032714844</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
@@ -61757,7 +61757,7 @@
     </row>
     <row r="2278">
       <c r="A2278" s="1" t="n">
-        <v>46052.4675694444</v>
+        <v>46052.3333333333</v>
       </c>
       <c r="B2278" t="n">
         <v>163</v>
@@ -61778,6 +61778,32 @@
         <v>734</v>
       </c>
       <c r="H2278" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" s="1" t="n">
+        <v>46055.5985763889</v>
+      </c>
+      <c r="B2279" t="n">
+        <v>466</v>
+      </c>
+      <c r="C2279" t="n">
+        <v>298</v>
+      </c>
+      <c r="D2279" t="n">
+        <v>297</v>
+      </c>
+      <c r="E2279" t="n">
+        <v>297</v>
+      </c>
+      <c r="F2279" t="n">
+        <v>297</v>
+      </c>
+      <c r="G2279" t="s">
+        <v>734</v>
+      </c>
+      <c r="H2279" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104431152344</t>
+    <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
     <t xml:space="preserve">359.914916992188</t>
@@ -56,10 +56,10 @@
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824859619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.7001953125</t>
+    <t xml:space="preserve">339.824829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">334.138977050781</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622772216797</t>
+    <t xml:space="preserve">332.622741699219</t>
   </si>
   <si>
     <t xml:space="preserve">338.119079589844</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">338.308624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071929931641</t>
+    <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">373.940002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077209472656</t>
+    <t xml:space="preserve">373.939971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
@@ -137,19 +137,19 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
+    <t xml:space="preserve">361.620666503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
     <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">362.947326660156</t>
+    <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -61783,7 +61783,7 @@
     </row>
     <row r="2279">
       <c r="A2279" s="1" t="n">
-        <v>46055.5985763889</v>
+        <v>46055.3333333333</v>
       </c>
       <c r="B2279" t="n">
         <v>466</v>
@@ -61804,6 +61804,32 @@
         <v>734</v>
       </c>
       <c r="H2279" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" s="1" t="n">
+        <v>46056.4601273148</v>
+      </c>
+      <c r="B2280" t="n">
+        <v>97</v>
+      </c>
+      <c r="C2280" t="n">
+        <v>298</v>
+      </c>
+      <c r="D2280" t="n">
+        <v>297</v>
+      </c>
+      <c r="E2280" t="n">
+        <v>297</v>
+      </c>
+      <c r="F2280" t="n">
+        <v>298</v>
+      </c>
+      <c r="G2280" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2280" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -61809,7 +61809,7 @@
     </row>
     <row r="2280">
       <c r="A2280" s="1" t="n">
-        <v>46056.4601273148</v>
+        <v>46056.3333333333</v>
       </c>
       <c r="B2280" t="n">
         <v>97</v>
@@ -61830,6 +61830,32 @@
         <v>360</v>
       </c>
       <c r="H2280" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" s="1" t="n">
+        <v>46057.4446412037</v>
+      </c>
+      <c r="B2281" t="n">
+        <v>31</v>
+      </c>
+      <c r="C2281" t="n">
+        <v>297</v>
+      </c>
+      <c r="D2281" t="n">
+        <v>297</v>
+      </c>
+      <c r="E2281" t="n">
+        <v>297</v>
+      </c>
+      <c r="F2281" t="n">
+        <v>297</v>
+      </c>
+      <c r="G2281" t="s">
+        <v>734</v>
+      </c>
+      <c r="H2281" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -61835,7 +61835,7 @@
     </row>
     <row r="2281">
       <c r="A2281" s="1" t="n">
-        <v>46057.4446412037</v>
+        <v>46057.3333333333</v>
       </c>
       <c r="B2281" t="n">
         <v>31</v>
@@ -61856,6 +61856,32 @@
         <v>734</v>
       </c>
       <c r="H2281" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" s="1" t="n">
+        <v>46058.5630787037</v>
+      </c>
+      <c r="B2282" t="n">
+        <v>495</v>
+      </c>
+      <c r="C2282" t="n">
+        <v>298</v>
+      </c>
+      <c r="D2282" t="n">
+        <v>297</v>
+      </c>
+      <c r="E2282" t="n">
+        <v>298</v>
+      </c>
+      <c r="F2282" t="n">
+        <v>297</v>
+      </c>
+      <c r="G2282" t="s">
+        <v>734</v>
+      </c>
+      <c r="H2282" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104400634766</t>
+    <t xml:space="preserve">360.104431152344</t>
   </si>
   <si>
     <t xml:space="preserve">359.914916992188</t>
@@ -56,10 +56,10 @@
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.700225830078</t>
+    <t xml:space="preserve">339.824859619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.7001953125</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">334.138977050781</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622741699219</t>
+    <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
     <t xml:space="preserve">338.119079589844</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">338.30859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071960449219</t>
+    <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">373.939971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077178955078</t>
+    <t xml:space="preserve">373.940002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077209472656</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
@@ -137,19 +137,19 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620666503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
+    <t xml:space="preserve">361.620635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
   </si>
   <si>
     <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -61861,7 +61861,7 @@
     </row>
     <row r="2282">
       <c r="A2282" s="1" t="n">
-        <v>46058.5630787037</v>
+        <v>46058.3333333333</v>
       </c>
       <c r="B2282" t="n">
         <v>495</v>
@@ -61882,6 +61882,32 @@
         <v>734</v>
       </c>
       <c r="H2282" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" s="1" t="n">
+        <v>46059.6666550926</v>
+      </c>
+      <c r="B2283" t="n">
+        <v>426</v>
+      </c>
+      <c r="C2283" t="n">
+        <v>298</v>
+      </c>
+      <c r="D2283" t="n">
+        <v>298</v>
+      </c>
+      <c r="E2283" t="n">
+        <v>298</v>
+      </c>
+      <c r="F2283" t="n">
+        <v>298</v>
+      </c>
+      <c r="G2283" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2283" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104431152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">360.104400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824859619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.7001953125</t>
+    <t xml:space="preserve">339.824829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">334.139007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
+    <t xml:space="preserve">331.675109863281</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151550292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.30859375</t>
+    <t xml:space="preserve">341.151519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071929931641</t>
+    <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">375.077178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
@@ -61887,10 +61887,10 @@
     </row>
     <row r="2283">
       <c r="A2283" s="1" t="n">
-        <v>46059.6666550926</v>
+        <v>46059.3333333333</v>
       </c>
       <c r="B2283" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C2283" t="n">
         <v>298</v>
@@ -61908,6 +61908,32 @@
         <v>360</v>
       </c>
       <c r="H2283" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" s="1" t="n">
+        <v>46062.6166666667</v>
+      </c>
+      <c r="B2284" t="n">
+        <v>196</v>
+      </c>
+      <c r="C2284" t="n">
+        <v>298</v>
+      </c>
+      <c r="D2284" t="n">
+        <v>298</v>
+      </c>
+      <c r="E2284" t="n">
+        <v>298</v>
+      </c>
+      <c r="F2284" t="n">
+        <v>298</v>
+      </c>
+      <c r="G2284" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2284" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,19 +44,19 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398651123047</t>
+    <t xml:space="preserve">358.398681640625</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -71,34 +71,34 @@
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">332.622772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727478027344</t>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727447509766</t>
   </si>
   <si>
     <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">343.804931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.438446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.151519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.308624267578</t>
+    <t xml:space="preserve">343.804962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.4384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.151550292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.30859375</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046813964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785034179688</t>
+    <t xml:space="preserve">343.046844482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785064697266</t>
   </si>
   <si>
     <t xml:space="preserve">369.580841064453</t>
@@ -119,37 +119,37 @@
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071960449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.940002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">371.476135253906</t>
+    <t xml:space="preserve">357.071929931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.939971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077209472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">371.476165771484</t>
   </si>
   <si>
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -61913,7 +61913,7 @@
     </row>
     <row r="2284">
       <c r="A2284" s="1" t="n">
-        <v>46062.6166666667</v>
+        <v>46062.3333333333</v>
       </c>
       <c r="B2284" t="n">
         <v>196</v>
@@ -61934,6 +61934,32 @@
         <v>360</v>
       </c>
       <c r="H2284" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" s="1" t="n">
+        <v>46063.6209027778</v>
+      </c>
+      <c r="B2285" t="n">
+        <v>77</v>
+      </c>
+      <c r="C2285" t="n">
+        <v>298</v>
+      </c>
+      <c r="D2285" t="n">
+        <v>298</v>
+      </c>
+      <c r="E2285" t="n">
+        <v>298</v>
+      </c>
+      <c r="F2285" t="n">
+        <v>298</v>
+      </c>
+      <c r="G2285" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2285" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -61939,7 +61939,7 @@
     </row>
     <row r="2285">
       <c r="A2285" s="1" t="n">
-        <v>46063.6209027778</v>
+        <v>46063.3333333333</v>
       </c>
       <c r="B2285" t="n">
         <v>77</v>
@@ -61960,6 +61960,32 @@
         <v>360</v>
       </c>
       <c r="H2285" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" s="1" t="n">
+        <v>46064.6666898148</v>
+      </c>
+      <c r="B2286" t="n">
+        <v>282</v>
+      </c>
+      <c r="C2286" t="n">
+        <v>298</v>
+      </c>
+      <c r="D2286" t="n">
+        <v>298</v>
+      </c>
+      <c r="E2286" t="n">
+        <v>298</v>
+      </c>
+      <c r="F2286" t="n">
+        <v>298</v>
+      </c>
+      <c r="G2286" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2286" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398681640625</t>
+    <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099182128906</t>
+    <t xml:space="preserve">342.099212646484</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
@@ -74,31 +74,31 @@
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727447509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.804962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.4384765625</t>
+    <t xml:space="preserve">338.119110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366241455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.804931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.438415527344</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
+    <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -107,61 +107,61 @@
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046844482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785064697266</t>
+    <t xml:space="preserve">343.046813964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528503417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.071929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.939971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077209472656</t>
+    <t xml:space="preserve">370.528533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.071960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.940002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">371.476165771484</t>
+    <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496032714844</t>
+    <t xml:space="preserve">367.496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -61965,7 +61965,7 @@
     </row>
     <row r="2286">
       <c r="A2286" s="1" t="n">
-        <v>46064.6666898148</v>
+        <v>46064.3333333333</v>
       </c>
       <c r="B2286" t="n">
         <v>282</v>
@@ -61986,6 +61986,32 @@
         <v>360</v>
       </c>
       <c r="H2286" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" s="1" t="n">
+        <v>46065.6745023148</v>
+      </c>
+      <c r="B2287" t="n">
+        <v>338</v>
+      </c>
+      <c r="C2287" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2287" t="n">
+        <v>298</v>
+      </c>
+      <c r="E2287" t="n">
+        <v>298</v>
+      </c>
+      <c r="F2287" t="n">
+        <v>298</v>
+      </c>
+      <c r="G2287" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2287" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -61991,7 +61991,7 @@
     </row>
     <row r="2287">
       <c r="A2287" s="1" t="n">
-        <v>46065.6745023148</v>
+        <v>46065.3333333333</v>
       </c>
       <c r="B2287" t="n">
         <v>338</v>
@@ -62012,6 +62012,32 @@
         <v>360</v>
       </c>
       <c r="H2287" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" s="1" t="n">
+        <v>46066.4214583333</v>
+      </c>
+      <c r="B2288" t="n">
+        <v>271</v>
+      </c>
+      <c r="C2288" t="n">
+        <v>298</v>
+      </c>
+      <c r="D2288" t="n">
+        <v>298</v>
+      </c>
+      <c r="E2288" t="n">
+        <v>298</v>
+      </c>
+      <c r="F2288" t="n">
+        <v>298</v>
+      </c>
+      <c r="G2288" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2288" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -62017,7 +62017,7 @@
     </row>
     <row r="2288">
       <c r="A2288" s="1" t="n">
-        <v>46066.4214583333</v>
+        <v>46066.3333333333</v>
       </c>
       <c r="B2288" t="n">
         <v>271</v>
@@ -62038,6 +62038,32 @@
         <v>360</v>
       </c>
       <c r="H2288" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" s="1" t="n">
+        <v>46069.654212963</v>
+      </c>
+      <c r="B2289" t="n">
+        <v>229</v>
+      </c>
+      <c r="C2289" t="n">
+        <v>298</v>
+      </c>
+      <c r="D2289" t="n">
+        <v>298</v>
+      </c>
+      <c r="E2289" t="n">
+        <v>298</v>
+      </c>
+      <c r="F2289" t="n">
+        <v>298</v>
+      </c>
+      <c r="G2289" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2289" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">360.104431152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -59,46 +59,46 @@
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.700225830078</t>
+    <t xml:space="preserve">345.7001953125</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099212646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.139007568359</t>
+    <t xml:space="preserve">342.099182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.138977050781</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119110107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366241455078</t>
+    <t xml:space="preserve">338.119079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438415527344</t>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
+    <t xml:space="preserve">338.30859375</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.071960449219</t>
+    <t xml:space="preserve">370.528503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077178955078</t>
+    <t xml:space="preserve">375.077209472656</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
@@ -140,22 +140,22 @@
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496002197266</t>
+    <t xml:space="preserve">367.496032714844</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
@@ -62043,7 +62043,7 @@
     </row>
     <row r="2289">
       <c r="A2289" s="1" t="n">
-        <v>46069.654212963</v>
+        <v>46069.3333333333</v>
       </c>
       <c r="B2289" t="n">
         <v>229</v>
@@ -62064,6 +62064,32 @@
         <v>360</v>
       </c>
       <c r="H2289" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" s="1" t="n">
+        <v>46070.6516203704</v>
+      </c>
+      <c r="B2290" t="n">
+        <v>210</v>
+      </c>
+      <c r="C2290" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2290" t="n">
+        <v>298</v>
+      </c>
+      <c r="E2290" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2290" t="n">
+        <v>298</v>
+      </c>
+      <c r="G2290" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2290" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104431152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">360.104400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -59,46 +59,46 @@
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.7001953125</t>
+    <t xml:space="preserve">345.700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.138977050781</t>
+    <t xml:space="preserve">342.099212646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">338.119110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366241455078</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438446044922</t>
+    <t xml:space="preserve">350.438415527344</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
+    <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528503417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.071929931641</t>
+    <t xml:space="preserve">370.528533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077209472656</t>
+    <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
@@ -140,22 +140,22 @@
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496032714844</t>
+    <t xml:space="preserve">367.496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
@@ -62069,7 +62069,7 @@
     </row>
     <row r="2290">
       <c r="A2290" s="1" t="n">
-        <v>46070.6516203704</v>
+        <v>46070.3333333333</v>
       </c>
       <c r="B2290" t="n">
         <v>210</v>
@@ -62090,6 +62090,32 @@
         <v>360</v>
       </c>
       <c r="H2290" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" s="1" t="n">
+        <v>46071.6595833333</v>
+      </c>
+      <c r="B2291" t="n">
+        <v>27</v>
+      </c>
+      <c r="C2291" t="n">
+        <v>298</v>
+      </c>
+      <c r="D2291" t="n">
+        <v>298</v>
+      </c>
+      <c r="E2291" t="n">
+        <v>298</v>
+      </c>
+      <c r="F2291" t="n">
+        <v>298</v>
+      </c>
+      <c r="G2291" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2291" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">360.104431152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -59,46 +59,46 @@
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.700225830078</t>
+    <t xml:space="preserve">345.7001953125</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099212646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.139007568359</t>
+    <t xml:space="preserve">342.099182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.138977050781</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119110107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366241455078</t>
+    <t xml:space="preserve">338.119079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438415527344</t>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
+    <t xml:space="preserve">338.30859375</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.071960449219</t>
+    <t xml:space="preserve">370.528503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077178955078</t>
+    <t xml:space="preserve">375.077209472656</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
@@ -140,22 +140,22 @@
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496002197266</t>
+    <t xml:space="preserve">367.496032714844</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
@@ -62095,7 +62095,7 @@
     </row>
     <row r="2291">
       <c r="A2291" s="1" t="n">
-        <v>46071.6595833333</v>
+        <v>46071.3333333333</v>
       </c>
       <c r="B2291" t="n">
         <v>27</v>
@@ -62116,6 +62116,32 @@
         <v>360</v>
       </c>
       <c r="H2291" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" s="1" t="n">
+        <v>46072.6122916667</v>
+      </c>
+      <c r="B2292" t="n">
+        <v>465</v>
+      </c>
+      <c r="C2292" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2292" t="n">
+        <v>298</v>
+      </c>
+      <c r="E2292" t="n">
+        <v>298</v>
+      </c>
+      <c r="F2292" t="n">
+        <v>299</v>
+      </c>
+      <c r="G2292" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2292" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398651123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">360.104431152344</t>
+    <t xml:space="preserve">358.398681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
     <t xml:space="preserve">359.914916992188</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.7001953125</t>
+    <t xml:space="preserve">345.700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
+    <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
-    <t xml:space="preserve">330.727478027344</t>
+    <t xml:space="preserve">330.727447509766</t>
   </si>
   <si>
     <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">343.804931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.438446044922</t>
+    <t xml:space="preserve">343.804962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.4384765625</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046813964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785034179688</t>
+    <t xml:space="preserve">343.046844482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785064697266</t>
   </si>
   <si>
     <t xml:space="preserve">369.580841064453</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.940002441406</t>
+    <t xml:space="preserve">369.391326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
     <t xml:space="preserve">375.077209472656</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">371.476135253906</t>
+    <t xml:space="preserve">371.476165771484</t>
   </si>
   <si>
     <t xml:space="preserve">361.620635986328</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -62121,7 +62121,7 @@
     </row>
     <row r="2292">
       <c r="A2292" s="1" t="n">
-        <v>46072.6122916667</v>
+        <v>46072.3333333333</v>
       </c>
       <c r="B2292" t="n">
         <v>465</v>
@@ -62142,6 +62142,32 @@
         <v>374</v>
       </c>
       <c r="H2292" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" s="1" t="n">
+        <v>46073.6310069444</v>
+      </c>
+      <c r="B2293" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2293" t="n">
+        <v>298</v>
+      </c>
+      <c r="D2293" t="n">
+        <v>298</v>
+      </c>
+      <c r="E2293" t="n">
+        <v>298</v>
+      </c>
+      <c r="F2293" t="n">
+        <v>298</v>
+      </c>
+      <c r="G2293" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2293" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -62147,7 +62147,7 @@
     </row>
     <row r="2293">
       <c r="A2293" s="1" t="n">
-        <v>46073.6310069444</v>
+        <v>46073.3333333333</v>
       </c>
       <c r="B2293" t="n">
         <v>3</v>
@@ -62168,6 +62168,32 @@
         <v>360</v>
       </c>
       <c r="H2293" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" s="1" t="n">
+        <v>46076.6593981481</v>
+      </c>
+      <c r="B2294" t="n">
+        <v>97</v>
+      </c>
+      <c r="C2294" t="n">
+        <v>298</v>
+      </c>
+      <c r="D2294" t="n">
+        <v>298</v>
+      </c>
+      <c r="E2294" t="n">
+        <v>298</v>
+      </c>
+      <c r="F2294" t="n">
+        <v>298</v>
+      </c>
+      <c r="G2294" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2294" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398681640625</t>
+    <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099182128906</t>
+    <t xml:space="preserve">342.099212646484</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
@@ -74,31 +74,31 @@
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727447509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.804962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.4384765625</t>
+    <t xml:space="preserve">338.119110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366241455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.804931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.438415527344</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
+    <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -107,61 +107,61 @@
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046844482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785064697266</t>
+    <t xml:space="preserve">343.046813964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528503417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.071929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.939971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077209472656</t>
+    <t xml:space="preserve">370.528533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.071960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.940002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">371.476165771484</t>
+    <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496032714844</t>
+    <t xml:space="preserve">367.496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -62173,7 +62173,7 @@
     </row>
     <row r="2294">
       <c r="A2294" s="1" t="n">
-        <v>46076.6593981481</v>
+        <v>46076.3333333333</v>
       </c>
       <c r="B2294" t="n">
         <v>97</v>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">360.104431152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -59,46 +59,46 @@
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.700225830078</t>
+    <t xml:space="preserve">345.7001953125</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099212646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.139007568359</t>
+    <t xml:space="preserve">342.099182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.138977050781</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119110107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366241455078</t>
+    <t xml:space="preserve">338.119079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438415527344</t>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
+    <t xml:space="preserve">338.30859375</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.071960449219</t>
+    <t xml:space="preserve">370.528503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077178955078</t>
+    <t xml:space="preserve">375.077209472656</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
@@ -140,22 +140,22 @@
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496002197266</t>
+    <t xml:space="preserve">367.496032714844</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
@@ -62197,6 +62197,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2295">
+      <c r="A2295" s="1" t="n">
+        <v>46077.3333333333</v>
+      </c>
+      <c r="B2295" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2295" t="n">
+        <v>298</v>
+      </c>
+      <c r="D2295" t="n">
+        <v>298</v>
+      </c>
+      <c r="E2295" t="n">
+        <v>298</v>
+      </c>
+      <c r="F2295" t="n">
+        <v>298</v>
+      </c>
+      <c r="G2295" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2295" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" s="1" t="n">
+        <v>46078.6913888889</v>
+      </c>
+      <c r="B2296" t="n">
+        <v>195</v>
+      </c>
+      <c r="C2296" t="n">
+        <v>298</v>
+      </c>
+      <c r="D2296" t="n">
+        <v>298</v>
+      </c>
+      <c r="E2296" t="n">
+        <v>298</v>
+      </c>
+      <c r="F2296" t="n">
+        <v>298</v>
+      </c>
+      <c r="G2296" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2296" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104431152344</t>
+    <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.627990722656</t>
+    <t xml:space="preserve">350.628021240234</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.7001953125</t>
+    <t xml:space="preserve">345.700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
+    <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
+    <t xml:space="preserve">331.675170898438</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">355.366180419922</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">338.308624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,49 +110,49 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">347.785064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.940002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">357.071960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.939971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">361.620666503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313873291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -62225,7 +62225,7 @@
     </row>
     <row r="2296">
       <c r="A2296" s="1" t="n">
-        <v>46078.6913888889</v>
+        <v>46078.3333333333</v>
       </c>
       <c r="B2296" t="n">
         <v>195</v>
@@ -62246,6 +62246,32 @@
         <v>360</v>
       </c>
       <c r="H2296" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" s="1" t="n">
+        <v>46079.6323148148</v>
+      </c>
+      <c r="B2297" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C2297" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2297" t="n">
+        <v>298</v>
+      </c>
+      <c r="E2297" t="n">
+        <v>298</v>
+      </c>
+      <c r="F2297" t="n">
+        <v>299</v>
+      </c>
+      <c r="G2297" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2297" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398651123047</t>
+    <t xml:space="preserve">358.398681640625</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.628021240234</t>
+    <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
@@ -74,52 +74,52 @@
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675170898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366180419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.804931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.438446044922</t>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727447509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.804962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.4384765625</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">338.30859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046813964844</t>
+    <t xml:space="preserve">343.046844482422</t>
   </si>
   <si>
     <t xml:space="preserve">347.785064697266</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071960449219</t>
+    <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">369.391326904297</t>
@@ -128,31 +128,31 @@
     <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">371.476135253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">361.620666503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313873291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">366.548431396484</t>
+    <t xml:space="preserve">375.077209472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">371.476165771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">361.620635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -62251,7 +62251,7 @@
     </row>
     <row r="2297">
       <c r="A2297" s="1" t="n">
-        <v>46079.6323148148</v>
+        <v>46079.3333333333</v>
       </c>
       <c r="B2297" t="n">
         <v>2100</v>
@@ -62272,6 +62272,32 @@
         <v>374</v>
       </c>
       <c r="H2297" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" s="1" t="n">
+        <v>46080.638912037</v>
+      </c>
+      <c r="B2298" t="n">
+        <v>31</v>
+      </c>
+      <c r="C2298" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2298" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2298" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2298" t="n">
+        <v>299</v>
+      </c>
+      <c r="G2298" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2298" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">360.104400634766</t>
+    <t xml:space="preserve">358.398651123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">360.104431152344</t>
   </si>
   <si>
     <t xml:space="preserve">359.914916992188</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.700225830078</t>
+    <t xml:space="preserve">345.7001953125</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
+    <t xml:space="preserve">334.138977050781</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
-    <t xml:space="preserve">330.727447509766</t>
+    <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
     <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">343.804962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.4384765625</t>
+    <t xml:space="preserve">343.804931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046844482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785064697266</t>
+    <t xml:space="preserve">343.046813964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">369.580841064453</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.939971923828</t>
+    <t xml:space="preserve">369.391296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
     <t xml:space="preserve">375.077209472656</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">371.476165771484</t>
+    <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
     <t xml:space="preserve">361.620635986328</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -62277,7 +62277,7 @@
     </row>
     <row r="2298">
       <c r="A2298" s="1" t="n">
-        <v>46080.638912037</v>
+        <v>46080.3333333333</v>
       </c>
       <c r="B2298" t="n">
         <v>31</v>
@@ -62298,6 +62298,32 @@
         <v>374</v>
       </c>
       <c r="H2298" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" s="1" t="n">
+        <v>46083.6735532407</v>
+      </c>
+      <c r="B2299" t="n">
+        <v>294</v>
+      </c>
+      <c r="C2299" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2299" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2299" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2299" t="n">
+        <v>299</v>
+      </c>
+      <c r="G2299" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2299" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -62303,7 +62303,7 @@
     </row>
     <row r="2299">
       <c r="A2299" s="1" t="n">
-        <v>46083.6735532407</v>
+        <v>46083.3333333333</v>
       </c>
       <c r="B2299" t="n">
         <v>294</v>
@@ -62324,6 +62324,32 @@
         <v>374</v>
       </c>
       <c r="H2299" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" s="1" t="n">
+        <v>46084.6782291667</v>
+      </c>
+      <c r="B2300" t="n">
+        <v>534</v>
+      </c>
+      <c r="C2300" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2300" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2300" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2300" t="n">
+        <v>299</v>
+      </c>
+      <c r="G2300" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2300" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104431152344</t>
+    <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.627990722656</t>
+    <t xml:space="preserve">350.628021240234</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.7001953125</t>
+    <t xml:space="preserve">345.700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
+    <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
+    <t xml:space="preserve">331.675170898438</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">355.366180419922</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">338.308624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,49 +110,49 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">347.785064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.940002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">357.071960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.939971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">361.620666503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313873291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -62329,7 +62329,7 @@
     </row>
     <row r="2300">
       <c r="A2300" s="1" t="n">
-        <v>46084.6782291667</v>
+        <v>46084.3333333333</v>
       </c>
       <c r="B2300" t="n">
         <v>534</v>
@@ -62350,6 +62350,32 @@
         <v>374</v>
       </c>
       <c r="H2300" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" s="1" t="n">
+        <v>46085.691099537</v>
+      </c>
+      <c r="B2301" t="n">
+        <v>1467</v>
+      </c>
+      <c r="C2301" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2301" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2301" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2301" t="n">
+        <v>299</v>
+      </c>
+      <c r="G2301" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2301" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -62355,7 +62355,7 @@
     </row>
     <row r="2301">
       <c r="A2301" s="1" t="n">
-        <v>46085.691099537</v>
+        <v>46085.3333333333</v>
       </c>
       <c r="B2301" t="n">
         <v>1467</v>
@@ -62376,6 +62376,32 @@
         <v>374</v>
       </c>
       <c r="H2301" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" s="1" t="n">
+        <v>46086.5628472222</v>
+      </c>
+      <c r="B2302" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2302" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2302" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2302" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2302" t="n">
+        <v>299</v>
+      </c>
+      <c r="G2302" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2302" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,10 +50,10 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914916992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.628021240234</t>
+    <t xml:space="preserve">359.914886474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099182128906</t>
+    <t xml:space="preserve">342.099212646484</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
@@ -77,22 +77,22 @@
     <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
-    <t xml:space="preserve">345.889770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675170898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366180419922</t>
+    <t xml:space="preserve">345.889801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366241455078</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438446044922</t>
+    <t xml:space="preserve">350.438415527344</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,34 +110,34 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785064697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580871582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">370.528503417969</t>
+    <t xml:space="preserve">347.785034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">370.528533935547</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.939971923828</t>
+    <t xml:space="preserve">369.391296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620666503906</t>
+    <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,22 +146,22 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313873291016</t>
+    <t xml:space="preserve">356.313812255859</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548431396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.496032714844</t>
+    <t xml:space="preserve">366.548400878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -62381,7 +62381,7 @@
     </row>
     <row r="2302">
       <c r="A2302" s="1" t="n">
-        <v>46086.5628472222</v>
+        <v>46086.3333333333</v>
       </c>
       <c r="B2302" t="n">
         <v>3</v>
@@ -62402,6 +62402,32 @@
         <v>374</v>
       </c>
       <c r="H2302" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" s="1" t="n">
+        <v>46087.6695023148</v>
+      </c>
+      <c r="B2303" t="n">
+        <v>28</v>
+      </c>
+      <c r="C2303" t="n">
+        <v>304</v>
+      </c>
+      <c r="D2303" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2303" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2303" t="n">
+        <v>300</v>
+      </c>
+      <c r="G2303" t="s">
+        <v>358</v>
+      </c>
+      <c r="H2303" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359.914886474609</t>
+    <t xml:space="preserve">360.104431152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -59,46 +59,46 @@
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.700225830078</t>
+    <t xml:space="preserve">345.7001953125</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099212646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.139007568359</t>
+    <t xml:space="preserve">342.099182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.138977050781</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119110107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366241455078</t>
+    <t xml:space="preserve">338.119079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438415527344</t>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
+    <t xml:space="preserve">338.30859375</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.071960449219</t>
+    <t xml:space="preserve">370.528503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">369.391296386719</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077178955078</t>
+    <t xml:space="preserve">375.077209472656</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
@@ -140,22 +140,22 @@
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496002197266</t>
+    <t xml:space="preserve">367.496032714844</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
@@ -62407,7 +62407,7 @@
     </row>
     <row r="2303">
       <c r="A2303" s="1" t="n">
-        <v>46087.6695023148</v>
+        <v>46087.3333333333</v>
       </c>
       <c r="B2303" t="n">
         <v>28</v>
@@ -62428,6 +62428,32 @@
         <v>358</v>
       </c>
       <c r="H2303" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" s="1" t="n">
+        <v>46090.6389930556</v>
+      </c>
+      <c r="B2304" t="n">
+        <v>188</v>
+      </c>
+      <c r="C2304" t="n">
+        <v>301</v>
+      </c>
+      <c r="D2304" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2304" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2304" t="n">
+        <v>299</v>
+      </c>
+      <c r="G2304" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2304" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">360.104431152344</t>
+    <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.627990722656</t>
+    <t xml:space="preserve">350.628021240234</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.7001953125</t>
+    <t xml:space="preserve">345.700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
+    <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
+    <t xml:space="preserve">331.675170898438</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">355.366180419922</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">338.308624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,49 +110,49 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">347.785064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.940002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">357.071960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.939971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">361.620666503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313873291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -62433,7 +62433,7 @@
     </row>
     <row r="2304">
       <c r="A2304" s="1" t="n">
-        <v>46090.6389930556</v>
+        <v>46090.3333333333</v>
       </c>
       <c r="B2304" t="n">
         <v>188</v>
@@ -62454,6 +62454,32 @@
         <v>374</v>
       </c>
       <c r="H2304" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" s="1" t="n">
+        <v>46091.5718171296</v>
+      </c>
+      <c r="B2305" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2305" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2305" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2305" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2305" t="n">
+        <v>299</v>
+      </c>
+      <c r="G2305" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2305" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -53,10 +53,10 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.628021240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">350.627990722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675170898438</t>
+    <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.366180419922</t>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785064697266</t>
+    <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">369.580871582031</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391326904297</t>
+    <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313873291016</t>
+    <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548431396484</t>
+    <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -62459,7 +62459,7 @@
     </row>
     <row r="2305">
       <c r="A2305" s="1" t="n">
-        <v>46091.5718171296</v>
+        <v>46091.3333333333</v>
       </c>
       <c r="B2305" t="n">
         <v>10</v>
@@ -62480,6 +62480,32 @@
         <v>374</v>
       </c>
       <c r="H2305" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" s="1" t="n">
+        <v>46092.5305671296</v>
+      </c>
+      <c r="B2306" t="n">
+        <v>61</v>
+      </c>
+      <c r="C2306" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2306" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2306" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2306" t="n">
+        <v>299</v>
+      </c>
+      <c r="G2306" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2306" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
+    <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
     <t xml:space="preserve">332.622741699219</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
+    <t xml:space="preserve">331.675109863281</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151550292969</t>
+    <t xml:space="preserve">341.151519775391</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
@@ -125,19 +125,19 @@
     <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">373.939971923828</t>
+    <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620666503906</t>
+    <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313842773438</t>
+    <t xml:space="preserve">356.313812255859</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -62485,7 +62485,7 @@
     </row>
     <row r="2306">
       <c r="A2306" s="1" t="n">
-        <v>46092.5305671296</v>
+        <v>46092.3333333333</v>
       </c>
       <c r="B2306" t="n">
         <v>61</v>
@@ -62506,6 +62506,32 @@
         <v>374</v>
       </c>
       <c r="H2306" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" s="1" t="n">
+        <v>46093.4219328704</v>
+      </c>
+      <c r="B2307" t="n">
+        <v>227</v>
+      </c>
+      <c r="C2307" t="n">
+        <v>305</v>
+      </c>
+      <c r="D2307" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2307" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2307" t="n">
+        <v>300</v>
+      </c>
+      <c r="G2307" t="s">
+        <v>358</v>
+      </c>
+      <c r="H2307" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="736">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -2217,6 +2217,9 @@
   </si>
   <si>
     <t xml:space="preserve">297</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
   </si>
 </sst>
 </file>
@@ -62511,7 +62514,7 @@
     </row>
     <row r="2307">
       <c r="A2307" s="1" t="n">
-        <v>46093.4219328704</v>
+        <v>46093.3333333333</v>
       </c>
       <c r="B2307" t="n">
         <v>227</v>
@@ -62532,6 +62535,56 @@
         <v>358</v>
       </c>
       <c r="H2307" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" s="1" t="n">
+        <v>46094.3333333333</v>
+      </c>
+      <c r="B2308" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2308" t="n">
+        <v>300</v>
+      </c>
+      <c r="D2308" t="n">
+        <v>300</v>
+      </c>
+      <c r="E2308" t="n">
+        <v>300</v>
+      </c>
+      <c r="F2308"/>
+      <c r="G2308" t="s">
+        <v>735</v>
+      </c>
+      <c r="H2308" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" s="1" t="n">
+        <v>46094.5022337963</v>
+      </c>
+      <c r="B2309" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2309" t="n">
+        <v>300</v>
+      </c>
+      <c r="D2309" t="n">
+        <v>300</v>
+      </c>
+      <c r="E2309" t="n">
+        <v>300</v>
+      </c>
+      <c r="F2309" t="n">
+        <v>300</v>
+      </c>
+      <c r="G2309" t="s">
+        <v>358</v>
+      </c>
+      <c r="H2309" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.627990722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">359.914916992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.628021240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622741699219</t>
+    <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
     <t xml:space="preserve">338.119110107422</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675109863281</t>
+    <t xml:space="preserve">331.675170898438</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">355.366180419922</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151519775391</t>
+    <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">347.785064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.940002441406</t>
+    <t xml:space="preserve">369.391326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
+    <t xml:space="preserve">361.620666503906</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313812255859</t>
+    <t xml:space="preserve">356.313873291016</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -62554,9 +62554,11 @@
       <c r="E2308" t="n">
         <v>300</v>
       </c>
-      <c r="F2308"/>
+      <c r="F2308" t="n">
+        <v>300</v>
+      </c>
       <c r="G2308" t="s">
-        <v>735</v>
+        <v>358</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62564,27 +62566,51 @@
     </row>
     <row r="2309">
       <c r="A2309" s="1" t="n">
-        <v>46094.5022337963</v>
+        <v>46097.3333333333</v>
       </c>
       <c r="B2309" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C2309" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D2309" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E2309" t="n">
-        <v>300</v>
-      </c>
-      <c r="F2309" t="n">
-        <v>300</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="F2309"/>
       <c r="G2309" t="s">
-        <v>358</v>
+        <v>735</v>
       </c>
       <c r="H2309" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" s="1" t="n">
+        <v>46097.5977662037</v>
+      </c>
+      <c r="B2310" t="n">
+        <v>50</v>
+      </c>
+      <c r="C2310" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2310" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2310" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2310" t="n">
+        <v>299</v>
+      </c>
+      <c r="G2310" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2310" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="735">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -53,10 +53,10 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.628021240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">350.627990722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675170898438</t>
+    <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.366180419922</t>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785064697266</t>
+    <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">369.580871582031</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391326904297</t>
+    <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313873291016</t>
+    <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548431396484</t>
+    <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -2217,9 +2217,6 @@
   </si>
   <si>
     <t xml:space="preserve">297</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
   </si>
 </sst>
 </file>
@@ -62580,37 +62577,13 @@
       <c r="E2309" t="n">
         <v>299</v>
       </c>
-      <c r="F2309"/>
+      <c r="F2309" t="n">
+        <v>299</v>
+      </c>
       <c r="G2309" t="s">
-        <v>735</v>
+        <v>374</v>
       </c>
       <c r="H2309" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2310">
-      <c r="A2310" s="1" t="n">
-        <v>46097.5977662037</v>
-      </c>
-      <c r="B2310" t="n">
-        <v>50</v>
-      </c>
-      <c r="C2310" t="n">
-        <v>299</v>
-      </c>
-      <c r="D2310" t="n">
-        <v>299</v>
-      </c>
-      <c r="E2310" t="n">
-        <v>299</v>
-      </c>
-      <c r="F2310" t="n">
-        <v>299</v>
-      </c>
-      <c r="G2310" t="s">
-        <v>374</v>
-      </c>
-      <c r="H2310" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="736">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398651123047</t>
+    <t xml:space="preserve">358.398681640625</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622741699219</t>
+    <t xml:space="preserve">334.139007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
     <t xml:space="preserve">338.119079589844</t>
@@ -83,73 +83,73 @@
     <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
-    <t xml:space="preserve">330.727478027344</t>
+    <t xml:space="preserve">330.727447509766</t>
   </si>
   <si>
     <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">343.804931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.438446044922</t>
+    <t xml:space="preserve">343.804962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.4384765625</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">338.30859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046813964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">343.046844482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071960449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391296386719</t>
+    <t xml:space="preserve">357.071929931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391326904297</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077178955078</t>
+    <t xml:space="preserve">375.077209472656</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">371.476135253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">361.620666503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
+    <t xml:space="preserve">371.476165771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">361.620635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
   </si>
   <si>
     <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
@@ -2217,6 +2217,9 @@
   </si>
   <si>
     <t xml:space="preserve">297</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
   </si>
 </sst>
 </file>
@@ -62587,6 +62590,82 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2310">
+      <c r="A2310" s="1" t="n">
+        <v>46098.3333333333</v>
+      </c>
+      <c r="B2310" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2310" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2310" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2310" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2310" t="n">
+        <v>299</v>
+      </c>
+      <c r="G2310" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2310" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" s="1" t="n">
+        <v>46099.3333333333</v>
+      </c>
+      <c r="B2311" t="n">
+        <v>32</v>
+      </c>
+      <c r="C2311" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2311" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2311" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2311"/>
+      <c r="G2311" t="s">
+        <v>735</v>
+      </c>
+      <c r="H2311" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" s="1" t="n">
+        <v>46099.4486226852</v>
+      </c>
+      <c r="B2312" t="n">
+        <v>32</v>
+      </c>
+      <c r="C2312" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2312" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2312" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2312" t="n">
+        <v>299</v>
+      </c>
+      <c r="G2312" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2312" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398681640625</t>
+    <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099182128906</t>
+    <t xml:space="preserve">342.099212646484</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
@@ -74,31 +74,31 @@
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.889770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.675140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727447509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.804962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.4384765625</t>
+    <t xml:space="preserve">338.119110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.889801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.675109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366241455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.804931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.438415527344</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
+    <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -107,61 +107,61 @@
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046844482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785064697266</t>
+    <t xml:space="preserve">343.046813964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528503417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.071929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.939971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077209472656</t>
+    <t xml:space="preserve">370.528533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.071960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.940002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">371.476165771484</t>
+    <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496032714844</t>
+    <t xml:space="preserve">367.496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -62632,9 +62632,11 @@
       <c r="E2311" t="n">
         <v>299</v>
       </c>
-      <c r="F2311"/>
+      <c r="F2311" t="n">
+        <v>299</v>
+      </c>
       <c r="G2311" t="s">
-        <v>735</v>
+        <v>374</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62642,10 +62644,10 @@
     </row>
     <row r="2312">
       <c r="A2312" s="1" t="n">
-        <v>46099.4486226852</v>
+        <v>46100.3333333333</v>
       </c>
       <c r="B2312" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C2312" t="n">
         <v>299</v>
@@ -62656,13 +62658,37 @@
       <c r="E2312" t="n">
         <v>299</v>
       </c>
-      <c r="F2312" t="n">
+      <c r="F2312"/>
+      <c r="G2312" t="s">
+        <v>735</v>
+      </c>
+      <c r="H2312" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" s="1" t="n">
+        <v>46100.3752893519</v>
+      </c>
+      <c r="B2313" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2313" t="n">
         <v>299</v>
       </c>
-      <c r="G2312" t="s">
+      <c r="D2313" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2313" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2313" t="n">
+        <v>299</v>
+      </c>
+      <c r="G2313" t="s">
         <v>374</v>
       </c>
-      <c r="H2312" t="s">
+      <c r="H2313" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="735">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -65,37 +65,37 @@
     <t xml:space="preserve">346.458343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">342.099212646484</t>
+    <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622772216797</t>
+    <t xml:space="preserve">332.622741699219</t>
   </si>
   <si>
     <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
-    <t xml:space="preserve">345.889801025391</t>
+    <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
     <t xml:space="preserve">331.675109863281</t>
   </si>
   <si>
-    <t xml:space="preserve">330.727508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366241455078</t>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">350.438415527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.151550292969</t>
+    <t xml:space="preserve">350.438446044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.151519775391</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">370.528533935547</t>
+    <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
     <t xml:space="preserve">357.071960449219</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875122070312</t>
+    <t xml:space="preserve">367.875091552734</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">367.496002197266</t>
+    <t xml:space="preserve">367.496032714844</t>
   </si>
   <si>
     <t xml:space="preserve">364.842620849609</t>
@@ -2217,9 +2217,6 @@
   </si>
   <si>
     <t xml:space="preserve">297</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
   </si>
 </sst>
 </file>
@@ -62658,37 +62655,13 @@
       <c r="E2312" t="n">
         <v>299</v>
       </c>
-      <c r="F2312"/>
+      <c r="F2312" t="n">
+        <v>299</v>
+      </c>
       <c r="G2312" t="s">
-        <v>735</v>
+        <v>374</v>
       </c>
       <c r="H2312" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2313">
-      <c r="A2313" s="1" t="n">
-        <v>46100.3752893519</v>
-      </c>
-      <c r="B2313" t="n">
-        <v>3</v>
-      </c>
-      <c r="C2313" t="n">
-        <v>299</v>
-      </c>
-      <c r="D2313" t="n">
-        <v>299</v>
-      </c>
-      <c r="E2313" t="n">
-        <v>299</v>
-      </c>
-      <c r="F2313" t="n">
-        <v>299</v>
-      </c>
-      <c r="G2313" t="s">
-        <v>374</v>
-      </c>
-      <c r="H2313" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="736">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,13 +50,13 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.627990722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">359.914916992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.628021240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622741699219</t>
+    <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
     <t xml:space="preserve">338.119110107422</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675109863281</t>
+    <t xml:space="preserve">331.675170898438</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">355.366180419922</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151519775391</t>
+    <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">347.785064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.940002441406</t>
+    <t xml:space="preserve">369.391326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
+    <t xml:space="preserve">361.620666503906</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313812255859</t>
+    <t xml:space="preserve">356.313873291016</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
@@ -2217,6 +2217,9 @@
   </si>
   <si>
     <t xml:space="preserve">297</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
   </si>
 </sst>
 </file>
@@ -62665,6 +62668,82 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2313">
+      <c r="A2313" s="1" t="n">
+        <v>46101.3333333333</v>
+      </c>
+      <c r="B2313" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2313" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2313" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2313" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2313" t="n">
+        <v>299</v>
+      </c>
+      <c r="G2313" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2313" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" s="1" t="n">
+        <v>46104.3333333333</v>
+      </c>
+      <c r="B2314" t="n">
+        <v>128</v>
+      </c>
+      <c r="C2314" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2314" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2314" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2314"/>
+      <c r="G2314" t="s">
+        <v>735</v>
+      </c>
+      <c r="H2314" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" s="1" t="n">
+        <v>46104.6546412037</v>
+      </c>
+      <c r="B2315" t="n">
+        <v>128</v>
+      </c>
+      <c r="C2315" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2315" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2315" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2315" t="n">
+        <v>299</v>
+      </c>
+      <c r="G2315" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2315" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="735">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398651123047</t>
+    <t xml:space="preserve">358.398681640625</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.628021240234</t>
+    <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
@@ -74,52 +74,52 @@
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675170898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.366180419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.804931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.438446044922</t>
+    <t xml:space="preserve">331.675140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727447509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.3662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.804962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.4384765625</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">338.30859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046813964844</t>
+    <t xml:space="preserve">343.046844482422</t>
   </si>
   <si>
     <t xml:space="preserve">347.785064697266</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071960449219</t>
+    <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">369.391326904297</t>
@@ -128,31 +128,31 @@
     <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">371.476135253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">361.620666503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313873291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947357177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">366.548431396484</t>
+    <t xml:space="preserve">375.077209472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">371.476165771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">361.620635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -2217,9 +2217,6 @@
   </si>
   <si>
     <t xml:space="preserve">297</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
   </si>
 </sst>
 </file>
@@ -62710,37 +62707,13 @@
       <c r="E2314" t="n">
         <v>299</v>
       </c>
-      <c r="F2314"/>
+      <c r="F2314" t="n">
+        <v>299</v>
+      </c>
       <c r="G2314" t="s">
-        <v>735</v>
+        <v>374</v>
       </c>
       <c r="H2314" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2315">
-      <c r="A2315" s="1" t="n">
-        <v>46104.6546412037</v>
-      </c>
-      <c r="B2315" t="n">
-        <v>128</v>
-      </c>
-      <c r="C2315" t="n">
-        <v>299</v>
-      </c>
-      <c r="D2315" t="n">
-        <v>299</v>
-      </c>
-      <c r="E2315" t="n">
-        <v>299</v>
-      </c>
-      <c r="F2315" t="n">
-        <v>299</v>
-      </c>
-      <c r="G2315" t="s">
-        <v>374</v>
-      </c>
-      <c r="H2315" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -62717,6 +62717,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2315">
+      <c r="A2315" s="1" t="n">
+        <v>46105.3333333333</v>
+      </c>
+      <c r="B2315" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2315" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2315" t="n">
+        <v>299</v>
+      </c>
+      <c r="E2315" t="n">
+        <v>299</v>
+      </c>
+      <c r="F2315" t="n">
+        <v>299</v>
+      </c>
+      <c r="G2315" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2315" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,19 +44,19 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398681640625</t>
+    <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914916992188</t>
+    <t xml:space="preserve">359.914886474609</t>
   </si>
   <si>
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -71,34 +71,34 @@
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">332.622741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727447509766</t>
+    <t xml:space="preserve">331.675109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
     <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">343.804962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.4384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.151550292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.30859375</t>
+    <t xml:space="preserve">343.804931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.438446044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.151519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
     <t xml:space="preserve">336.413330078125</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046844482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785064697266</t>
+    <t xml:space="preserve">343.046813964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">369.580841064453</t>
@@ -119,37 +119,37 @@
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.939971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.077209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875122070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">371.476165771484</t>
+    <t xml:space="preserve">357.071960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.940002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.077178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875091552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
     <t xml:space="preserve">361.620635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">360.104400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">359.914886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.627990722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">359.914916992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.628021240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">334.139007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">332.622741699219</t>
+    <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
     <t xml:space="preserve">338.119110107422</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675109863281</t>
+    <t xml:space="preserve">331.675170898438</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.3662109375</t>
+    <t xml:space="preserve">355.366180419922</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">341.151519775391</t>
+    <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
     <t xml:space="preserve">338.308624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">347.785064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.940002441406</t>
+    <t xml:space="preserve">369.391326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
     <t xml:space="preserve">375.077178955078</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
-    <t xml:space="preserve">361.620635986328</t>
+    <t xml:space="preserve">361.620666503906</t>
   </si>
   <si>
     <t xml:space="preserve">375.266693115234</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313812255859</t>
+    <t xml:space="preserve">356.313873291016</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814758300781</t>
+    <t xml:space="preserve">372.814727783203</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766235351562</t>
+    <t xml:space="preserve">386.766204833984</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101959228516</t>
+    <t xml:space="preserve">370.101928710938</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.479034423828</t>
+    <t xml:space="preserve">389.47900390625</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852752685547</t>
+    <t xml:space="preserve">387.541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852783203125</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745269775391</t>
+    <t xml:space="preserve">424.745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025329589844</t>
+    <t xml:space="preserve">472.025299072266</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.361022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516723632812</t>
+    <t xml:space="preserve">473.769226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.360992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516754150391</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.06005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028869628906</t>
+    <t xml:space="preserve">446.060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028900146484</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316131591797</t>
+    <t xml:space="preserve">444.316101074219</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478729248047</t>
+    <t xml:space="preserve">445.478698730469</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606903076172</t>
+    <t xml:space="preserve">416.606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270874023438</t>
+    <t xml:space="preserve">489.270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.16357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897155761719</t>
+    <t xml:space="preserve">518.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.163513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897125244141</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828247070312</t>
+    <t xml:space="preserve">434.240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828216552734</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814453125</t>
+    <t xml:space="preserve">428.814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914794921875</t>
+    <t xml:space="preserve">432.49609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357696533203</t>
+    <t xml:space="preserve">430.945892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413146972656</t>
+    <t xml:space="preserve">416.413116455078</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.250518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444274902344</t>
+    <t xml:space="preserve">414.669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.25048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444244384766</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925262451172</t>
+    <t xml:space="preserve">412.925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257385253906</t>
+    <t xml:space="preserve">416.994415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257415771484</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513427734375</t>
+    <t xml:space="preserve">410.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513458251953</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544586181641</t>
+    <t xml:space="preserve">418.544616699219</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319671630859</t>
+    <t xml:space="preserve">416.025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073822021484</t>
+    <t xml:space="preserve">458.073791503906</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928283691406</t>
+    <t xml:space="preserve">488.302001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.461059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.520050048828</t>
+    <t xml:space="preserve">481.52001953125</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644622802734</t>
+    <t xml:space="preserve">477.644653320312</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800384521484</t>
+    <t xml:space="preserve">472.800354003906</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679077148438</t>
+    <t xml:space="preserve">507.679107666016</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398681640625</t>
+    <t xml:space="preserve">358.398651123047</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.627990722656</t>
+    <t xml:space="preserve">350.628021240234</t>
   </si>
   <si>
     <t xml:space="preserve">339.824859619141</t>
@@ -74,52 +74,52 @@
     <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.119079589844</t>
+    <t xml:space="preserve">338.119110107422</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.727447509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.3662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.804962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.4384765625</t>
+    <t xml:space="preserve">331.675170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.727478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.366180419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.804931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.30859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413330078125</t>
+    <t xml:space="preserve">338.308624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413299560547</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046844482422</t>
+    <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
     <t xml:space="preserve">347.785064697266</t>
   </si>
   <si>
-    <t xml:space="preserve">369.580841064453</t>
+    <t xml:space="preserve">369.580871582031</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071929931641</t>
+    <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
     <t xml:space="preserve">369.391326904297</t>
@@ -128,31 +128,31 @@
     <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.875122070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">371.476165771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">361.620635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356.313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362.947326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">366.548400878906</t>
+    <t xml:space="preserve">375.077178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.875091552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">371.476135253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">361.620666503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356.313873291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362.947357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366.548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -53,10 +53,10 @@
     <t xml:space="preserve">359.914916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">350.628021240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.824859619141</t>
+    <t xml:space="preserve">350.627990722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.824829101562</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.119110107422</t>
+    <t xml:space="preserve">334.138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">345.889770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">331.675170898438</t>
+    <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
     <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">355.366180419922</t>
+    <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
     <t xml:space="preserve">343.804931640625</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">343.046813964844</t>
   </si>
   <si>
-    <t xml:space="preserve">347.785064697266</t>
+    <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">369.580871582031</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">357.071960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391326904297</t>
+    <t xml:space="preserve">369.391296386719</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">375.077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">367.875091552734</t>
+    <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
     <t xml:space="preserve">371.476135253906</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">367.685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">356.313873291016</t>
+    <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
     <t xml:space="preserve">362.947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">366.548431396484</t>
+    <t xml:space="preserve">366.548400878906</t>
   </si>
   <si>
     <t xml:space="preserve">367.496032714844</t>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398651123047</t>
+    <t xml:space="preserve">358.398681640625</t>
   </si>
   <si>
     <t xml:space="preserve">360.104400634766</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">350.627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">339.824829101562</t>
+    <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
     <t xml:space="preserve">345.700225830078</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.138977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.622741699219</t>
+    <t xml:space="preserve">334.139007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.622772216797</t>
   </si>
   <si>
     <t xml:space="preserve">338.119079589844</t>
@@ -83,73 +83,73 @@
     <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
-    <t xml:space="preserve">330.727478027344</t>
+    <t xml:space="preserve">330.727447509766</t>
   </si>
   <si>
     <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">343.804931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.438446044922</t>
+    <t xml:space="preserve">343.804962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.4384765625</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.308624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.413299560547</t>
+    <t xml:space="preserve">338.30859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046813964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.580871582031</t>
+    <t xml:space="preserve">343.046844482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">370.528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">357.071960449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369.391296386719</t>
+    <t xml:space="preserve">357.071929931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.391326904297</t>
   </si>
   <si>
     <t xml:space="preserve">373.939971923828</t>
   </si>
   <si>
-    <t xml:space="preserve">375.077178955078</t>
+    <t xml:space="preserve">375.077209472656</t>
   </si>
   <si>
     <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">371.476135253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">361.620666503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.266693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">367.685546875</t>
+    <t xml:space="preserve">371.476165771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">361.620635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.266723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">367.685577392578</t>
   </si>
   <si>
     <t xml:space="preserve">356.313842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">362.947357177734</t>
+    <t xml:space="preserve">362.947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">366.548400878906</t>

--- a/data/HI.MI.xlsx
+++ b/data/HI.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">HI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">358.398681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">360.104400634766</t>
+    <t xml:space="preserve">358.398651123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">360.104431152344</t>
   </si>
   <si>
     <t xml:space="preserve">359.914916992188</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">339.824859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">345.700225830078</t>
+    <t xml:space="preserve">345.7001953125</t>
   </si>
   <si>
     <t xml:space="preserve">346.458343505859</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">342.099182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">334.139007568359</t>
+    <t xml:space="preserve">334.138977050781</t>
   </si>
   <si>
     <t xml:space="preserve">332.622772216797</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">331.675140380859</t>
   </si>
   <si>
-    <t xml:space="preserve">330.727447509766</t>
+    <t xml:space="preserve">330.727478027344</t>
   </si>
   <si>
     <t xml:space="preserve">355.3662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">343.804962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.4384765625</t>
+    <t xml:space="preserve">343.804931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.438446044922</t>
   </si>
   <si>
     <t xml:space="preserve">341.151550292969</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">346.647888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">343.046844482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.785064697266</t>
+    <t xml:space="preserve">343.046813964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">369.580841064453</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">357.071929931641</t>
   </si>
   <si>
-    <t xml:space="preserve">369.391326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373.939971923828</t>
+    <t xml:space="preserve">369.391296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373.940002441406</t>
   </si>
   <si>
     <t xml:space="preserve">375.077209472656</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">367.875122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">371.476165771484</t>
+    <t xml:space="preserve">371.476135253906</t>
   </si>
   <si>
     <t xml:space="preserve">361.620635986328</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">364.842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">372.814727783203</t>
+    <t xml:space="preserve">372.814758300781</t>
   </si>
   <si>
     <t xml:space="preserve">379.790466308594</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">381.534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">386.766204833984</t>
+    <t xml:space="preserve">386.766235351562</t>
   </si>
   <si>
     <t xml:space="preserve">384.634735107422</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">367.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">370.101928710938</t>
+    <t xml:space="preserve">370.101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">369.326873779297</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">373.977355957031</t>
   </si>
   <si>
-    <t xml:space="preserve">389.47900390625</t>
+    <t xml:space="preserve">389.479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.292114257812</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">389.091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">387.541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.852783203125</t>
+    <t xml:space="preserve">387.541320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">379.984222412109</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">397.229827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">424.745300292969</t>
+    <t xml:space="preserve">424.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">420.676086425781</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">466.405944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">472.025299072266</t>
+    <t xml:space="preserve">472.025329589844</t>
   </si>
   <si>
     <t xml:space="preserve">465.243316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">473.769226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">455.360992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.516754150391</t>
+    <t xml:space="preserve">473.769256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">455.361022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.516723632812</t>
   </si>
   <si>
     <t xml:space="preserve">468.343658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">446.060028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447.028900146484</t>
+    <t xml:space="preserve">446.06005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">454.392181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">444.316101074219</t>
+    <t xml:space="preserve">444.316131591797</t>
   </si>
   <si>
     <t xml:space="preserve">448.385284423828</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">445.672515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">445.478698730469</t>
+    <t xml:space="preserve">445.478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">412.731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">416.606872558594</t>
+    <t xml:space="preserve">416.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">428.233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">489.270904541016</t>
+    <t xml:space="preserve">489.270874023438</t>
   </si>
   <si>
     <t xml:space="preserve">497.021728515625</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">508.647979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">518.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508.163513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.772583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.897125244141</t>
+    <t xml:space="preserve">518.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.16357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.772552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">502.834838867188</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">445.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">434.240051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.828216552734</t>
+    <t xml:space="preserve">434.240020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">428.039367675781</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">435.596435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">428.814483642578</t>
+    <t xml:space="preserve">428.814453125</t>
   </si>
   <si>
     <t xml:space="preserve">443.541015625</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">434.433776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">432.49609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.914764404297</t>
+    <t xml:space="preserve">432.496063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">443.734771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">430.945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424.357727050781</t>
+    <t xml:space="preserve">430.945922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424.357696533203</t>
   </si>
   <si>
     <t xml:space="preserve">422.420013427734</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">446.447570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">416.413116455078</t>
+    <t xml:space="preserve">416.413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">419.901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">414.669189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.25048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.444244384766</t>
+    <t xml:space="preserve">414.669219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.250518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">411.762634277344</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">407.88720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">412.925231933594</t>
+    <t xml:space="preserve">412.925262451172</t>
   </si>
   <si>
     <t xml:space="preserve">417.575744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">416.994415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.257415771484</t>
+    <t xml:space="preserve">416.994445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">415.056732177734</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">406.143249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.513458251953</t>
+    <t xml:space="preserve">410.406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.748870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.513427734375</t>
   </si>
   <si>
     <t xml:space="preserve">414.475433349609</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">417.381988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">418.544616699219</t>
+    <t xml:space="preserve">418.544586181641</t>
   </si>
   <si>
     <t xml:space="preserve">411.56884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">416.025573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.319702148438</t>
+    <t xml:space="preserve">416.025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">404.20556640625</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">453.423309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">458.073791503906</t>
+    <t xml:space="preserve">458.073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">470.862670898438</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">472.219055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">488.302001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.461059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.928253173828</t>
+    <t xml:space="preserve">488.302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.616760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">492.177459716797</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">527.056091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">481.52001953125</t>
+    <t xml:space="preserve">481.520050048828</t>
   </si>
   <si>
     <t xml:space="preserve">480.551208496094</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">483.457794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">477.644653320312</t>
+    <t xml:space="preserve">477.644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">479.582336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">472.800354003906</t>
+    <t xml:space="preserve">472.800384521484</t>
   </si>
   <si>
     <t xml:space="preserve">464.080688476562</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">497.990570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">507.679107666016</t>
+    <t xml:space="preserve">507.679077148438</t>
   </si>
   <si>
     <t xml:space="preserve">491.453674316406</t>
